--- a/Plannings 2026 S25 v2.xlsx
+++ b/Plannings 2026 S25 v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7AA5A74F-8B5F-4333-8824-7AED61442DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{7AA5A74F-8B5F-4333-8824-7AED61442DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F922CC8-FB2A-42B5-8CED-F6F7D790AED3}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="140">
   <si>
     <t>Planning des salariés du 15/06/2026 au 21/06/2026</t>
   </si>
@@ -438,10 +438,10 @@
     <t>17:00/22:20</t>
   </si>
   <si>
-    <t>08:45/17:00</t>
-  </si>
-  <si>
     <t>17:45/23:40</t>
+  </si>
+  <si>
+    <t>08:45/17:45</t>
   </si>
 </sst>
 </file>
@@ -6861,7 +6861,7 @@
         <v>95</v>
       </c>
       <c r="H80" s="56" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -6893,16 +6893,14 @@
         <v>97</v>
       </c>
       <c r="B83" s="16"/>
-      <c r="C83" s="16"/>
-      <c r="D83" s="16"/>
-      <c r="E83" s="16"/>
-      <c r="F83" s="16"/>
-      <c r="G83" s="16" t="s">
+      <c r="C83" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="H83" s="37" t="s">
-        <v>81</v>
-      </c>
+      <c r="D83" s="60"/>
+      <c r="E83" s="60"/>
+      <c r="F83" s="60"/>
+      <c r="G83" s="60"/>
+      <c r="H83" s="61"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="65" t="s">
@@ -7017,7 +7015,7 @@
         <v>102</v>
       </c>
       <c r="H91" s="20" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
@@ -7112,7 +7110,7 @@
       <c r="H98" s="68"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="30">
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A7:A8"/>
@@ -7137,6 +7135,7 @@
     <mergeCell ref="A77:A78"/>
     <mergeCell ref="A79:A82"/>
     <mergeCell ref="A84:A85"/>
+    <mergeCell ref="C83:H83"/>
     <mergeCell ref="B15:H15"/>
     <mergeCell ref="B58:H58"/>
     <mergeCell ref="B56:H56"/>

--- a/Plannings 2026 S25 v2.xlsx
+++ b/Plannings 2026 S25 v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{7AA5A74F-8B5F-4333-8824-7AED61442DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F922CC8-FB2A-42B5-8CED-F6F7D790AED3}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{7AA5A74F-8B5F-4333-8824-7AED61442DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71C3B252-B6E7-4AF0-9872-A5BAA55BFE97}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="141">
   <si>
     <t>Planning des salariés du 15/06/2026 au 21/06/2026</t>
   </si>
@@ -111,12 +111,6 @@
     <t>CONRAD - stage David</t>
   </si>
   <si>
-    <t>11:35/15:45</t>
-  </si>
-  <si>
-    <t>11:30/17:00</t>
-  </si>
-  <si>
     <t>CRUZEL Quentin</t>
   </si>
   <si>
@@ -442,6 +436,15 @@
   </si>
   <si>
     <t>08:45/17:45</t>
+  </si>
+  <si>
+    <t>11:50/15:00</t>
+  </si>
+  <si>
+    <t>11:40/17:00</t>
+  </si>
+  <si>
+    <t>11:00/14:30</t>
   </si>
 </sst>
 </file>
@@ -880,7 +883,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1029,28 +1032,7 @@
     <xf numFmtId="0" fontId="15" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1104,6 +1086,15 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5300,6 +5291,446 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="24479250" y="15920357"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="112" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA0439F9-5649-46A3-9480-5566FF0BAC6B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="4200525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="113" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1EC9A592-C701-4C86-B7BB-A6FC1B972644}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="4200525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="114" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96921F9E-9A4B-4EC4-8F82-E4D6F6C508A7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="4581525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="115" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8DC2BC0-0087-4CBC-AD31-0DE6038C3D97}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="4962525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="116" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F96B865-2055-448D-BB5D-FAA41821368A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="4200525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="117" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9CBC38C-9C6E-4936-AC87-70C417552CF8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="4581525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="118" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B77FE16A-C9A5-4B77-9A7E-4E4F8CC0D09D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="4962525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="119" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49726ADD-927B-4B43-AC06-B0AA1A867AE5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2438400" y="4200525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="120" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86C49609-422E-4477-987A-FD88977743FA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3048000" y="4200525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="121" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F4D0BED-8C6F-42BC-B29A-4CC92C58BA57}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3657600" y="4200525"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5688,48 +6119,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="70" t="s">
+      <c r="B1" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="70" t="s">
+      <c r="B2" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="E3" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="F3" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="D3" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="E3" s="13" t="s">
+      <c r="G3" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="F3" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>136</v>
-      </c>
       <c r="H3" s="13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5759,7 +6190,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="65" t="s">
+      <c r="A5" s="58" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="15"/>
@@ -5773,7 +6204,7 @@
       <c r="H5" s="17"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="67"/>
+      <c r="A6" s="60"/>
       <c r="B6" s="18"/>
       <c r="C6" s="19"/>
       <c r="D6" s="19"/>
@@ -5785,7 +6216,7 @@
       <c r="H6" s="20"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="65" t="s">
+      <c r="A7" s="58" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="16"/>
@@ -5799,7 +6230,7 @@
       <c r="H7" s="17"/>
     </row>
     <row r="8" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="67"/>
+      <c r="A8" s="60"/>
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
       <c r="D8" s="19" t="s">
@@ -5811,7 +6242,7 @@
       <c r="H8" s="20"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="65" t="s">
+      <c r="A9" s="58" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="31" t="s">
@@ -5829,7 +6260,7 @@
       <c r="H9" s="17"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="66"/>
+      <c r="A10" s="59"/>
       <c r="B10" s="32" t="s">
         <v>19</v>
       </c>
@@ -5845,7 +6276,7 @@
       <c r="H10" s="21"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="66"/>
+      <c r="A11" s="59"/>
       <c r="B11" s="2" t="s">
         <v>15</v>
       </c>
@@ -5859,7 +6290,7 @@
       <c r="H11" s="21"/>
     </row>
     <row r="12" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="67"/>
+      <c r="A12" s="60"/>
       <c r="B12" s="19" t="s">
         <v>23</v>
       </c>
@@ -5873,7 +6304,7 @@
       <c r="H12" s="20"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="65" t="s">
+      <c r="A13" s="58" t="s">
         <v>25</v>
       </c>
       <c r="B13" s="16" t="s">
@@ -5887,7 +6318,7 @@
       <c r="H13" s="17"/>
     </row>
     <row r="14" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="67"/>
+      <c r="A14" s="60"/>
       <c r="B14" s="19" t="s">
         <v>26</v>
       </c>
@@ -5902,115 +6333,119 @@
       <c r="A15" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="59"/>
-      <c r="C15" s="60"/>
-      <c r="D15" s="60"/>
-      <c r="E15" s="60"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="60"/>
-      <c r="H15" s="61"/>
+      <c r="B15" s="52"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="53"/>
+      <c r="H15" s="54"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="65" t="s">
+      <c r="A16" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="54" t="s">
+      <c r="B16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="54" t="s">
+      <c r="C16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="54" t="s">
+      <c r="D16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="54" t="s">
+      <c r="E16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="54" t="s">
+      <c r="F16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="54"/>
-      <c r="H16" s="55"/>
+      <c r="G16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="1"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="66"/>
-      <c r="B17" s="51" t="s">
+      <c r="A17" s="68"/>
+      <c r="B17" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H17" s="1"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="68"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="69" t="s">
+        <v>127</v>
+      </c>
+      <c r="D18" s="69" t="s">
+        <v>127</v>
+      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="68"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="70" t="s">
+        <v>128</v>
+      </c>
+      <c r="D19" s="70" t="s">
+        <v>128</v>
+      </c>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="68"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="68"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="58" t="s">
         <v>29</v>
-      </c>
-      <c r="C17" s="51" t="s">
-        <v>128</v>
-      </c>
-      <c r="D17" s="51" t="s">
-        <v>128</v>
-      </c>
-      <c r="E17" s="51" t="s">
-        <v>30</v>
-      </c>
-      <c r="F17" s="51" t="s">
-        <v>30</v>
-      </c>
-      <c r="G17" s="51"/>
-      <c r="H17" s="56"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="66"/>
-      <c r="B18" s="51"/>
-      <c r="C18" s="52" t="s">
-        <v>129</v>
-      </c>
-      <c r="D18" s="52" t="s">
-        <v>129</v>
-      </c>
-      <c r="E18" s="51"/>
-      <c r="F18" s="51"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="56"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="66"/>
-      <c r="B19" s="51"/>
-      <c r="C19" s="53" t="s">
-        <v>130</v>
-      </c>
-      <c r="D19" s="53" t="s">
-        <v>130</v>
-      </c>
-      <c r="E19" s="51"/>
-      <c r="F19" s="51"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="56"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="66"/>
-      <c r="B20" s="51"/>
-      <c r="C20" s="50" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" s="50" t="s">
-        <v>15</v>
-      </c>
-      <c r="E20" s="51"/>
-      <c r="F20" s="51"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="56"/>
-    </row>
-    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="67"/>
-      <c r="B21" s="57"/>
-      <c r="C21" s="57" t="s">
-        <v>131</v>
-      </c>
-      <c r="D21" s="57" t="s">
-        <v>131</v>
-      </c>
-      <c r="E21" s="57"/>
-      <c r="F21" s="57"/>
-      <c r="G21" s="57"/>
-      <c r="H21" s="58"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="65" t="s">
-        <v>31</v>
       </c>
       <c r="B22" s="16" t="s">
         <v>15</v>
@@ -6024,16 +6459,16 @@
         <v>15</v>
       </c>
       <c r="G22" s="35" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="66"/>
+      <c r="A23" s="59"/>
       <c r="B23" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>16</v>
@@ -6041,17 +6476,17 @@
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G23" s="36" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H23" s="41" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="66"/>
+      <c r="A24" s="59"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
@@ -6065,67 +6500,67 @@
       </c>
     </row>
     <row r="25" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="67"/>
+      <c r="A25" s="60"/>
       <c r="B25" s="19"/>
       <c r="C25" s="19"/>
       <c r="D25" s="19"/>
       <c r="E25" s="19"/>
       <c r="F25" s="19"/>
       <c r="G25" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="H25" s="51" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="58" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="H25" s="58" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="65" t="s">
+      <c r="C26" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="43" t="s">
-        <v>37</v>
-      </c>
-      <c r="C26" s="27" t="s">
-        <v>38</v>
-      </c>
       <c r="D26" s="27" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E26" s="27" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F26" s="16"/>
       <c r="G26" s="16"/>
       <c r="H26" s="17"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="66"/>
+      <c r="A27" s="59"/>
       <c r="B27" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="C27" s="28" t="s">
+      <c r="E27" s="28" t="s">
         <v>40</v>
-      </c>
-      <c r="D27" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="E27" s="28" t="s">
-        <v>42</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="21"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="66"/>
+      <c r="A28" s="59"/>
       <c r="B28" s="30" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C28" s="45" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D28" s="30" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>15</v>
@@ -6135,31 +6570,31 @@
       <c r="H28" s="21"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="66"/>
+      <c r="A29" s="59"/>
       <c r="B29" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="D29" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="C29" s="32" t="s">
+      <c r="E29" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="D29" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="21"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="66"/>
+      <c r="A30" s="59"/>
       <c r="B30" s="28"/>
       <c r="C30" s="30" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
@@ -6167,13 +6602,13 @@
       <c r="H30" s="21"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="66"/>
+      <c r="A31" s="59"/>
       <c r="B31" s="28"/>
       <c r="C31" s="28" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
@@ -6181,13 +6616,13 @@
       <c r="H31" s="21"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="66"/>
+      <c r="A32" s="59"/>
       <c r="B32" s="28"/>
       <c r="C32" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D32" s="30" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
@@ -6195,13 +6630,13 @@
       <c r="H32" s="21"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="66"/>
+      <c r="A33" s="59"/>
       <c r="B33" s="28"/>
       <c r="C33" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D33" s="28" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
@@ -6209,10 +6644,10 @@
       <c r="H33" s="21"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="66"/>
+      <c r="A34" s="59"/>
       <c r="B34" s="28"/>
       <c r="C34" s="30" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D34" s="28"/>
       <c r="E34" s="1"/>
@@ -6221,10 +6656,10 @@
       <c r="H34" s="21"/>
     </row>
     <row r="35" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="69"/>
+      <c r="A35" s="62"/>
       <c r="B35" s="28"/>
       <c r="C35" s="28" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D35" s="28"/>
       <c r="E35" s="1"/>
@@ -6233,8 +6668,8 @@
       <c r="H35" s="21"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="65" t="s">
-        <v>55</v>
+      <c r="A36" s="58" t="s">
+        <v>53</v>
       </c>
       <c r="B36" s="16"/>
       <c r="C36" s="16"/>
@@ -6249,11 +6684,11 @@
       <c r="H36" s="17"/>
     </row>
     <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="67"/>
+      <c r="A37" s="60"/>
       <c r="B37" s="19"/>
       <c r="C37" s="19"/>
       <c r="D37" s="29" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E37" s="19"/>
       <c r="F37" s="19"/>
@@ -6263,8 +6698,8 @@
       <c r="H37" s="20"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="65" t="s">
-        <v>56</v>
+      <c r="A38" s="58" t="s">
+        <v>54</v>
       </c>
       <c r="B38" s="27" t="s">
         <v>12</v>
@@ -6273,7 +6708,7 @@
         <v>15</v>
       </c>
       <c r="D38" s="27" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E38" s="16" t="s">
         <v>15</v>
@@ -6287,21 +6722,21 @@
       <c r="H38" s="17"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="66"/>
+      <c r="A39" s="59"/>
       <c r="B39" s="28" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D39" s="28" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F39" s="28" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G39" s="28" t="s">
         <v>13</v>
@@ -6309,7 +6744,7 @@
       <c r="H39" s="21"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="66"/>
+      <c r="A40" s="59"/>
       <c r="B40" s="28"/>
       <c r="C40" s="1"/>
       <c r="D40" s="2" t="s">
@@ -6323,25 +6758,25 @@
       <c r="H40" s="21"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="66"/>
+      <c r="A41" s="59"/>
       <c r="B41" s="28"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E41" s="1"/>
       <c r="F41" s="28"/>
       <c r="G41" s="28" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H41" s="21"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="66"/>
+      <c r="A42" s="59"/>
       <c r="B42" s="28"/>
       <c r="C42" s="1"/>
       <c r="D42" s="30" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E42" s="1"/>
       <c r="F42" s="28"/>
@@ -6349,11 +6784,11 @@
       <c r="H42" s="21"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="66"/>
+      <c r="A43" s="59"/>
       <c r="B43" s="28"/>
       <c r="C43" s="1"/>
       <c r="D43" s="28" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="28"/>
@@ -6361,11 +6796,11 @@
       <c r="H43" s="21"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="66"/>
+      <c r="A44" s="59"/>
       <c r="B44" s="28"/>
       <c r="C44" s="1"/>
       <c r="D44" s="46" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="28"/>
@@ -6373,11 +6808,11 @@
       <c r="H44" s="21"/>
     </row>
     <row r="45" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="67"/>
+      <c r="A45" s="60"/>
       <c r="B45" s="29"/>
       <c r="C45" s="19"/>
       <c r="D45" s="47" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E45" s="19"/>
       <c r="F45" s="29"/>
@@ -6385,8 +6820,8 @@
       <c r="H45" s="20"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="65" t="s">
-        <v>66</v>
+      <c r="A46" s="58" t="s">
+        <v>64</v>
       </c>
       <c r="B46" s="16"/>
       <c r="C46" s="16"/>
@@ -6401,11 +6836,11 @@
       <c r="H46" s="17"/>
     </row>
     <row r="47" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="67"/>
+      <c r="A47" s="60"/>
       <c r="B47" s="19"/>
       <c r="C47" s="19"/>
       <c r="D47" s="19" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E47" s="19" t="s">
         <v>16</v>
@@ -6415,69 +6850,69 @@
       <c r="H47" s="20"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="65" t="s">
-        <v>120</v>
+      <c r="A48" s="58" t="s">
+        <v>118</v>
       </c>
       <c r="B48" s="16"/>
       <c r="C48" s="16"/>
       <c r="D48" s="27" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E48" s="16"/>
       <c r="F48" s="16"/>
       <c r="G48" s="35" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H48" s="17"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="66"/>
+      <c r="A49" s="59"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="28" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="36" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H49" s="21"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="66"/>
+      <c r="A50" s="59"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
       <c r="G50" s="33" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H50" s="21"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="66"/>
+      <c r="A51" s="59"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="28" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="36" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H51" s="21"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="66"/>
+      <c r="A52" s="59"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
@@ -6485,11 +6920,11 @@
       <c r="H52" s="21"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="66"/>
+      <c r="A53" s="59"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
@@ -6497,11 +6932,11 @@
       <c r="H53" s="21"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="66"/>
+      <c r="A54" s="59"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
@@ -6509,11 +6944,11 @@
       <c r="H54" s="21"/>
     </row>
     <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="67"/>
+      <c r="A55" s="60"/>
       <c r="B55" s="19"/>
       <c r="C55" s="19"/>
       <c r="D55" s="19" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E55" s="19"/>
       <c r="F55" s="19"/>
@@ -6522,43 +6957,43 @@
     </row>
     <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="B56" s="62"/>
-      <c r="C56" s="63"/>
-      <c r="D56" s="63"/>
-      <c r="E56" s="63"/>
-      <c r="F56" s="63"/>
-      <c r="G56" s="63"/>
-      <c r="H56" s="64"/>
+        <v>71</v>
+      </c>
+      <c r="B56" s="55"/>
+      <c r="C56" s="56"/>
+      <c r="D56" s="56"/>
+      <c r="E56" s="56"/>
+      <c r="F56" s="56"/>
+      <c r="G56" s="56"/>
+      <c r="H56" s="57"/>
     </row>
     <row r="57" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="B57" s="59"/>
-      <c r="C57" s="60"/>
-      <c r="D57" s="60"/>
-      <c r="E57" s="60"/>
-      <c r="F57" s="60"/>
-      <c r="G57" s="60"/>
-      <c r="H57" s="61"/>
+        <v>72</v>
+      </c>
+      <c r="B57" s="52"/>
+      <c r="C57" s="53"/>
+      <c r="D57" s="53"/>
+      <c r="E57" s="53"/>
+      <c r="F57" s="53"/>
+      <c r="G57" s="53"/>
+      <c r="H57" s="54"/>
     </row>
     <row r="58" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="B58" s="59"/>
-      <c r="C58" s="60"/>
-      <c r="D58" s="60"/>
-      <c r="E58" s="60"/>
-      <c r="F58" s="60"/>
-      <c r="G58" s="60"/>
-      <c r="H58" s="61"/>
+        <v>73</v>
+      </c>
+      <c r="B58" s="52"/>
+      <c r="C58" s="53"/>
+      <c r="D58" s="53"/>
+      <c r="E58" s="53"/>
+      <c r="F58" s="53"/>
+      <c r="G58" s="53"/>
+      <c r="H58" s="54"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="65" t="s">
-        <v>76</v>
+      <c r="A59" s="58" t="s">
+        <v>74</v>
       </c>
       <c r="B59" s="16"/>
       <c r="C59" s="16"/>
@@ -6571,29 +7006,29 @@
       <c r="H59" s="17"/>
     </row>
     <row r="60" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="67"/>
+      <c r="A60" s="60"/>
       <c r="B60" s="19"/>
       <c r="C60" s="19"/>
       <c r="D60" s="19"/>
       <c r="E60" s="19"/>
       <c r="F60" s="29" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G60" s="19"/>
       <c r="H60" s="20"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="65" t="s">
-        <v>77</v>
+      <c r="A61" s="58" t="s">
+        <v>75</v>
       </c>
       <c r="B61" s="48" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C61" s="48" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D61" s="48" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E61" s="16"/>
       <c r="F61" s="16"/>
@@ -6601,15 +7036,15 @@
       <c r="H61" s="17"/>
     </row>
     <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="67"/>
+      <c r="A62" s="60"/>
       <c r="B62" s="47" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C62" s="47" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D62" s="47" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E62" s="19"/>
       <c r="F62" s="19"/>
@@ -6617,8 +7052,8 @@
       <c r="H62" s="20"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="65" t="s">
-        <v>80</v>
+      <c r="A63" s="58" t="s">
+        <v>78</v>
       </c>
       <c r="B63" s="16"/>
       <c r="C63" s="16"/>
@@ -6626,28 +7061,28 @@
       <c r="E63" s="16"/>
       <c r="F63" s="16"/>
       <c r="G63" s="35" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H63" s="17" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="66"/>
+      <c r="A64" s="59"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="36" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H64" s="21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="66"/>
+      <c r="A65" s="59"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
@@ -6655,11 +7090,11 @@
       <c r="F65" s="1"/>
       <c r="G65" s="36"/>
       <c r="H65" s="40" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="66"/>
+      <c r="A66" s="59"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
@@ -6667,11 +7102,11 @@
       <c r="F66" s="1"/>
       <c r="G66" s="36"/>
       <c r="H66" s="38" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="66"/>
+      <c r="A67" s="59"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
@@ -6683,7 +7118,7 @@
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="66"/>
+      <c r="A68" s="59"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
@@ -6691,11 +7126,11 @@
       <c r="F68" s="1"/>
       <c r="G68" s="36"/>
       <c r="H68" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="66"/>
+      <c r="A69" s="59"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
@@ -6703,11 +7138,11 @@
       <c r="F69" s="1"/>
       <c r="G69" s="36"/>
       <c r="H69" s="40" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="67"/>
+      <c r="A70" s="60"/>
       <c r="B70" s="19"/>
       <c r="C70" s="19"/>
       <c r="D70" s="19"/>
@@ -6715,12 +7150,12 @@
       <c r="F70" s="19"/>
       <c r="G70" s="34"/>
       <c r="H70" s="39" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="65" t="s">
-        <v>87</v>
+      <c r="A71" s="58" t="s">
+        <v>85</v>
       </c>
       <c r="B71" s="16"/>
       <c r="C71" s="48" t="s">
@@ -6733,10 +7168,10 @@
       <c r="H71" s="17"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="66"/>
+      <c r="A72" s="59"/>
       <c r="B72" s="1"/>
       <c r="C72" s="49" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
@@ -6745,10 +7180,10 @@
       <c r="H72" s="21"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="66"/>
+      <c r="A73" s="59"/>
       <c r="B73" s="1"/>
       <c r="C73" s="46" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
@@ -6757,10 +7192,10 @@
       <c r="H73" s="21"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="66"/>
+      <c r="A74" s="59"/>
       <c r="B74" s="1"/>
       <c r="C74" s="49" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
@@ -6769,7 +7204,7 @@
       <c r="H74" s="21"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="66"/>
+      <c r="A75" s="59"/>
       <c r="B75" s="1"/>
       <c r="C75" s="46" t="s">
         <v>22</v>
@@ -6781,10 +7216,10 @@
       <c r="H75" s="21"/>
     </row>
     <row r="76" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="67"/>
+      <c r="A76" s="60"/>
       <c r="B76" s="19"/>
       <c r="C76" s="47" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D76" s="19"/>
       <c r="E76" s="19"/>
@@ -6793,8 +7228,8 @@
       <c r="H76" s="20"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="65" t="s">
-        <v>90</v>
+      <c r="A77" s="58" t="s">
+        <v>88</v>
       </c>
       <c r="B77" s="16"/>
       <c r="C77" s="27" t="s">
@@ -6806,29 +7241,29 @@
         <v>12</v>
       </c>
       <c r="G77" s="33" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H77" s="17"/>
     </row>
     <row r="78" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="69"/>
+      <c r="A78" s="62"/>
       <c r="B78" s="1"/>
       <c r="C78" s="28" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
       <c r="F78" s="28" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G78" s="34" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H78" s="21"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="65" t="s">
-        <v>91</v>
+      <c r="A79" s="58" t="s">
+        <v>89</v>
       </c>
       <c r="B79" s="25"/>
       <c r="C79" s="25"/>
@@ -6837,7 +7272,7 @@
       </c>
       <c r="E79" s="16"/>
       <c r="F79" s="43" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G79" s="16" t="s">
         <v>15</v>
@@ -6847,25 +7282,25 @@
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="66"/>
+      <c r="A80" s="59"/>
       <c r="B80" s="12"/>
       <c r="C80" s="12"/>
       <c r="D80" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E80" s="1"/>
       <c r="F80" s="44" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="H80" s="56" t="s">
-        <v>139</v>
+        <v>93</v>
+      </c>
+      <c r="H80" s="50" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="66"/>
+      <c r="A81" s="59"/>
       <c r="B81" s="12"/>
       <c r="C81" s="12"/>
       <c r="D81" s="1"/>
@@ -6877,34 +7312,34 @@
       <c r="H81" s="21"/>
     </row>
     <row r="82" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="67"/>
+      <c r="A82" s="60"/>
       <c r="B82" s="26"/>
       <c r="C82" s="26"/>
       <c r="D82" s="19"/>
       <c r="E82" s="19"/>
       <c r="F82" s="19" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G82" s="19"/>
       <c r="H82" s="20"/>
     </row>
     <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="14" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B83" s="16"/>
-      <c r="C83" s="59" t="s">
+      <c r="C83" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="D83" s="60"/>
-      <c r="E83" s="60"/>
-      <c r="F83" s="60"/>
-      <c r="G83" s="60"/>
-      <c r="H83" s="61"/>
+      <c r="D83" s="53"/>
+      <c r="E83" s="53"/>
+      <c r="F83" s="53"/>
+      <c r="G83" s="53"/>
+      <c r="H83" s="54"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="65" t="s">
-        <v>98</v>
+      <c r="A84" s="58" t="s">
+        <v>96</v>
       </c>
       <c r="B84" s="16"/>
       <c r="C84" s="16"/>
@@ -6917,11 +7352,11 @@
       <c r="H84" s="17"/>
     </row>
     <row r="85" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="69"/>
+      <c r="A85" s="62"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
       <c r="D85" s="28" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
@@ -6930,31 +7365,31 @@
     </row>
     <row r="86" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="22" t="s">
-        <v>99</v>
-      </c>
-      <c r="B86" s="59"/>
-      <c r="C86" s="60"/>
-      <c r="D86" s="60"/>
-      <c r="E86" s="60"/>
-      <c r="F86" s="60"/>
-      <c r="G86" s="60"/>
-      <c r="H86" s="61"/>
+        <v>97</v>
+      </c>
+      <c r="B86" s="52"/>
+      <c r="C86" s="53"/>
+      <c r="D86" s="53"/>
+      <c r="E86" s="53"/>
+      <c r="F86" s="53"/>
+      <c r="G86" s="53"/>
+      <c r="H86" s="54"/>
     </row>
     <row r="87" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="B87" s="59"/>
-      <c r="C87" s="60"/>
-      <c r="D87" s="60"/>
-      <c r="E87" s="60"/>
-      <c r="F87" s="60"/>
-      <c r="G87" s="60"/>
-      <c r="H87" s="61"/>
+        <v>98</v>
+      </c>
+      <c r="B87" s="52"/>
+      <c r="C87" s="53"/>
+      <c r="D87" s="53"/>
+      <c r="E87" s="53"/>
+      <c r="F87" s="53"/>
+      <c r="G87" s="53"/>
+      <c r="H87" s="54"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="65" t="s">
-        <v>101</v>
+      <c r="A88" s="58" t="s">
+        <v>99</v>
       </c>
       <c r="B88" s="16"/>
       <c r="C88" s="16" t="s">
@@ -6966,17 +7401,17 @@
         <v>15</v>
       </c>
       <c r="G88" s="35" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H88" s="37" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="66"/>
+      <c r="A89" s="59"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D89" s="1"/>
       <c r="E89" s="1"/>
@@ -6984,14 +7419,14 @@
         <v>26</v>
       </c>
       <c r="G89" s="36" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H89" s="38" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="66"/>
+      <c r="A90" s="59"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
       <c r="D90" s="1"/>
@@ -7005,22 +7440,22 @@
       </c>
     </row>
     <row r="91" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="67"/>
+      <c r="A91" s="60"/>
       <c r="B91" s="19"/>
       <c r="C91" s="19"/>
       <c r="D91" s="19"/>
       <c r="E91" s="19"/>
       <c r="F91" s="19"/>
       <c r="G91" s="19" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H91" s="20" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="65" t="s">
-        <v>103</v>
+      <c r="A92" s="58" t="s">
+        <v>101</v>
       </c>
       <c r="B92" s="16"/>
       <c r="C92" s="16"/>
@@ -7030,30 +7465,30 @@
       <c r="E92" s="16"/>
       <c r="F92" s="16"/>
       <c r="G92" s="27" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H92" s="37" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="66"/>
+      <c r="A93" s="59"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
       <c r="D93" s="28" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E93" s="1"/>
       <c r="F93" s="1"/>
       <c r="G93" s="28" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H93" s="38" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="66"/>
+      <c r="A94" s="59"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
       <c r="D94" s="28"/>
@@ -7062,52 +7497,52 @@
       <c r="G94" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="H94" s="73"/>
+      <c r="H94" s="66"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="66"/>
+      <c r="A95" s="59"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
       <c r="D95" s="28"/>
       <c r="E95" s="1"/>
       <c r="F95" s="1"/>
       <c r="G95" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="H95" s="73"/>
+        <v>57</v>
+      </c>
+      <c r="H95" s="66"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A96" s="66"/>
+      <c r="A96" s="59"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
       <c r="D96" s="28"/>
       <c r="E96" s="1"/>
       <c r="F96" s="1"/>
       <c r="G96" s="33" t="s">
-        <v>81</v>
-      </c>
-      <c r="H96" s="73"/>
+        <v>79</v>
+      </c>
+      <c r="H96" s="66"/>
     </row>
     <row r="97" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="67"/>
+      <c r="A97" s="60"/>
       <c r="B97" s="19"/>
       <c r="C97" s="19"/>
       <c r="D97" s="29"/>
       <c r="E97" s="19"/>
       <c r="F97" s="19"/>
       <c r="G97" s="34" t="s">
-        <v>105</v>
-      </c>
-      <c r="H97" s="74"/>
+        <v>103</v>
+      </c>
+      <c r="H97" s="67"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B98" s="68"/>
-      <c r="C98" s="68"/>
-      <c r="D98" s="68"/>
-      <c r="E98" s="68"/>
-      <c r="F98" s="68"/>
-      <c r="G98" s="68"/>
-      <c r="H98" s="68"/>
+      <c r="B98" s="61"/>
+      <c r="C98" s="61"/>
+      <c r="D98" s="61"/>
+      <c r="E98" s="61"/>
+      <c r="F98" s="61"/>
+      <c r="G98" s="61"/>
+      <c r="H98" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -7159,36 +7594,36 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="71" t="s">
-        <v>106</v>
-      </c>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
+      <c r="B4" s="64" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="72" t="s">
-        <v>107</v>
-      </c>
-      <c r="C5" s="72"/>
-      <c r="D5" s="72"/>
-      <c r="E5" s="72"/>
+      <c r="B5" s="65" t="s">
+        <v>105</v>
+      </c>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>109</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -7295,7 +7730,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B13" s="7">
         <v>0</v>
@@ -7312,7 +7747,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B14" s="7">
         <v>0</v>
@@ -7329,7 +7764,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B15" s="7">
         <v>0</v>
@@ -7346,7 +7781,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B16" s="7">
         <v>0</v>
@@ -7363,7 +7798,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B17" s="7">
         <v>0</v>
@@ -7380,7 +7815,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B18" s="7">
         <v>0</v>
@@ -7397,7 +7832,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B19" s="7">
         <v>0</v>
@@ -7414,7 +7849,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B20" s="7">
         <v>0</v>
@@ -7431,7 +7866,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B21" s="7">
         <v>0</v>
@@ -7448,7 +7883,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B22" s="7">
         <v>0</v>
@@ -7465,7 +7900,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B23" s="7">
         <v>0</v>
@@ -7482,7 +7917,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B24" s="7">
         <v>0</v>
@@ -7499,7 +7934,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B25" s="7">
         <v>0</v>
@@ -7516,7 +7951,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B26" s="7">
         <v>0</v>
@@ -7533,7 +7968,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B27" s="7">
         <v>0</v>
@@ -7550,7 +7985,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B28" s="7">
         <v>0</v>
@@ -7567,7 +8002,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B29" s="7">
         <v>0</v>
@@ -7584,7 +8019,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B30" s="7">
         <v>0</v>
@@ -7601,7 +8036,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B31" s="7">
         <v>0</v>
@@ -7618,7 +8053,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B32" s="7">
         <v>0</v>
@@ -7635,7 +8070,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B33" s="7">
         <v>0</v>
@@ -7685,40 +8120,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/Plannings 2026 S25 v2.xlsx
+++ b/Plannings 2026 S25 v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{7AA5A74F-8B5F-4333-8824-7AED61442DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71C3B252-B6E7-4AF0-9872-A5BAA55BFE97}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{7AA5A74F-8B5F-4333-8824-7AED61442DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F922CC8-FB2A-42B5-8CED-F6F7D790AED3}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="140">
   <si>
     <t>Planning des salariés du 15/06/2026 au 21/06/2026</t>
   </si>
@@ -111,6 +111,12 @@
     <t>CONRAD - stage David</t>
   </si>
   <si>
+    <t>11:35/15:45</t>
+  </si>
+  <si>
+    <t>11:30/17:00</t>
+  </si>
+  <si>
     <t>CRUZEL Quentin</t>
   </si>
   <si>
@@ -436,15 +442,6 @@
   </si>
   <si>
     <t>08:45/17:45</t>
-  </si>
-  <si>
-    <t>11:50/15:00</t>
-  </si>
-  <si>
-    <t>11:40/17:00</t>
-  </si>
-  <si>
-    <t>11:00/14:30</t>
   </si>
 </sst>
 </file>
@@ -883,7 +880,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1032,7 +1029,28 @@
     <xf numFmtId="0" fontId="15" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1086,15 +1104,6 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5291,446 +5300,6 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="24479250" y="15920357"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="112" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA0439F9-5649-46A3-9480-5566FF0BAC6B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="609600" y="4200525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="113" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1EC9A592-C701-4C86-B7BB-A6FC1B972644}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1219200" y="4200525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="114" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96921F9E-9A4B-4EC4-8F82-E4D6F6C508A7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1219200" y="4581525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="115" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8DC2BC0-0087-4CBC-AD31-0DE6038C3D97}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1219200" y="4962525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="116" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F96B865-2055-448D-BB5D-FAA41821368A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1828800" y="4200525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="117" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9CBC38C-9C6E-4936-AC87-70C417552CF8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1828800" y="4581525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="118" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B77FE16A-C9A5-4B77-9A7E-4E4F8CC0D09D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1828800" y="4962525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="119" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49726ADD-927B-4B43-AC06-B0AA1A867AE5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2438400" y="4200525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="120" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86C49609-422E-4477-987A-FD88977743FA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3048000" y="4200525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="121" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F4D0BED-8C6F-42BC-B29A-4CC92C58BA57}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3657600" y="4200525"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6119,48 +5688,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="63" t="s">
+      <c r="B1" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="63" t="s">
+      <c r="B2" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="63"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="13" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6190,7 +5759,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="58" t="s">
+      <c r="A5" s="65" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="15"/>
@@ -6204,7 +5773,7 @@
       <c r="H5" s="17"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="60"/>
+      <c r="A6" s="67"/>
       <c r="B6" s="18"/>
       <c r="C6" s="19"/>
       <c r="D6" s="19"/>
@@ -6216,7 +5785,7 @@
       <c r="H6" s="20"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="58" t="s">
+      <c r="A7" s="65" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="16"/>
@@ -6230,7 +5799,7 @@
       <c r="H7" s="17"/>
     </row>
     <row r="8" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="60"/>
+      <c r="A8" s="67"/>
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
       <c r="D8" s="19" t="s">
@@ -6242,7 +5811,7 @@
       <c r="H8" s="20"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="58" t="s">
+      <c r="A9" s="65" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="31" t="s">
@@ -6260,7 +5829,7 @@
       <c r="H9" s="17"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="59"/>
+      <c r="A10" s="66"/>
       <c r="B10" s="32" t="s">
         <v>19</v>
       </c>
@@ -6276,7 +5845,7 @@
       <c r="H10" s="21"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="59"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="2" t="s">
         <v>15</v>
       </c>
@@ -6290,7 +5859,7 @@
       <c r="H11" s="21"/>
     </row>
     <row r="12" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="60"/>
+      <c r="A12" s="67"/>
       <c r="B12" s="19" t="s">
         <v>23</v>
       </c>
@@ -6304,7 +5873,7 @@
       <c r="H12" s="20"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="58" t="s">
+      <c r="A13" s="65" t="s">
         <v>25</v>
       </c>
       <c r="B13" s="16" t="s">
@@ -6318,7 +5887,7 @@
       <c r="H13" s="17"/>
     </row>
     <row r="14" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="60"/>
+      <c r="A14" s="67"/>
       <c r="B14" s="19" t="s">
         <v>26</v>
       </c>
@@ -6333,119 +5902,115 @@
       <c r="A15" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="52"/>
-      <c r="C15" s="53"/>
-      <c r="D15" s="53"/>
-      <c r="E15" s="53"/>
-      <c r="F15" s="53"/>
-      <c r="G15" s="53"/>
-      <c r="H15" s="54"/>
+      <c r="B15" s="59"/>
+      <c r="C15" s="60"/>
+      <c r="D15" s="60"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="61"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="68" t="s">
+      <c r="A16" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G16" s="54"/>
+      <c r="H16" s="55"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="66"/>
+      <c r="B17" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="D17" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="E17" s="51" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17" s="51" t="s">
+        <v>30</v>
+      </c>
+      <c r="G17" s="51"/>
+      <c r="H17" s="56"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="66"/>
+      <c r="B18" s="51"/>
+      <c r="C18" s="52" t="s">
+        <v>129</v>
+      </c>
+      <c r="D18" s="52" t="s">
+        <v>129</v>
+      </c>
+      <c r="E18" s="51"/>
+      <c r="F18" s="51"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="56"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="66"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="D19" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="E19" s="51"/>
+      <c r="F19" s="51"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="56"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="66"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="H16" s="1"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="68"/>
-      <c r="B17" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="H17" s="1"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="68"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="69" t="s">
-        <v>127</v>
-      </c>
-      <c r="D18" s="69" t="s">
-        <v>127</v>
-      </c>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="68"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="70" t="s">
-        <v>128</v>
-      </c>
-      <c r="D19" s="70" t="s">
-        <v>128</v>
-      </c>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="68"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="56"/>
     </row>
     <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="68"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
+      <c r="A21" s="67"/>
+      <c r="B21" s="57"/>
+      <c r="C21" s="57" t="s">
+        <v>131</v>
+      </c>
+      <c r="D21" s="57" t="s">
+        <v>131</v>
+      </c>
+      <c r="E21" s="57"/>
+      <c r="F21" s="57"/>
+      <c r="G21" s="57"/>
+      <c r="H21" s="58"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="58" t="s">
-        <v>29</v>
+      <c r="A22" s="65" t="s">
+        <v>31</v>
       </c>
       <c r="B22" s="16" t="s">
         <v>15</v>
@@ -6459,16 +6024,16 @@
         <v>15</v>
       </c>
       <c r="G22" s="35" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="59"/>
+      <c r="A23" s="66"/>
       <c r="B23" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>16</v>
@@ -6476,17 +6041,17 @@
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G23" s="36" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H23" s="41" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="59"/>
+      <c r="A24" s="66"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
@@ -6500,67 +6065,67 @@
       </c>
     </row>
     <row r="25" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="60"/>
+      <c r="A25" s="67"/>
       <c r="B25" s="19"/>
       <c r="C25" s="19"/>
       <c r="D25" s="19"/>
       <c r="E25" s="19"/>
       <c r="F25" s="19"/>
       <c r="G25" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="H25" s="51" t="s">
-        <v>135</v>
+        <v>35</v>
+      </c>
+      <c r="H25" s="58" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="58" t="s">
-        <v>34</v>
+      <c r="A26" s="65" t="s">
+        <v>36</v>
       </c>
       <c r="B26" s="43" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C26" s="27" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D26" s="27" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E26" s="27" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F26" s="16"/>
       <c r="G26" s="16"/>
       <c r="H26" s="17"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="59"/>
+      <c r="A27" s="66"/>
       <c r="B27" s="44" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C27" s="28" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D27" s="28" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E27" s="28" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="21"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="59"/>
+      <c r="A28" s="66"/>
       <c r="B28" s="30" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C28" s="45" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D28" s="30" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>15</v>
@@ -6570,31 +6135,31 @@
       <c r="H28" s="21"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="59"/>
+      <c r="A29" s="66"/>
       <c r="B29" s="28" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C29" s="32" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D29" s="28" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="21"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="59"/>
+      <c r="A30" s="66"/>
       <c r="B30" s="28"/>
       <c r="C30" s="30" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
@@ -6602,13 +6167,13 @@
       <c r="H30" s="21"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="59"/>
+      <c r="A31" s="66"/>
       <c r="B31" s="28"/>
       <c r="C31" s="28" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
@@ -6616,13 +6181,13 @@
       <c r="H31" s="21"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="59"/>
+      <c r="A32" s="66"/>
       <c r="B32" s="28"/>
       <c r="C32" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D32" s="30" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
@@ -6630,13 +6195,13 @@
       <c r="H32" s="21"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="59"/>
+      <c r="A33" s="66"/>
       <c r="B33" s="28"/>
       <c r="C33" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D33" s="28" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
@@ -6644,10 +6209,10 @@
       <c r="H33" s="21"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="59"/>
+      <c r="A34" s="66"/>
       <c r="B34" s="28"/>
       <c r="C34" s="30" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D34" s="28"/>
       <c r="E34" s="1"/>
@@ -6656,10 +6221,10 @@
       <c r="H34" s="21"/>
     </row>
     <row r="35" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="62"/>
+      <c r="A35" s="69"/>
       <c r="B35" s="28"/>
       <c r="C35" s="28" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D35" s="28"/>
       <c r="E35" s="1"/>
@@ -6668,8 +6233,8 @@
       <c r="H35" s="21"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="58" t="s">
-        <v>53</v>
+      <c r="A36" s="65" t="s">
+        <v>55</v>
       </c>
       <c r="B36" s="16"/>
       <c r="C36" s="16"/>
@@ -6684,11 +6249,11 @@
       <c r="H36" s="17"/>
     </row>
     <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="60"/>
+      <c r="A37" s="67"/>
       <c r="B37" s="19"/>
       <c r="C37" s="19"/>
       <c r="D37" s="29" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E37" s="19"/>
       <c r="F37" s="19"/>
@@ -6698,8 +6263,8 @@
       <c r="H37" s="20"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="58" t="s">
-        <v>54</v>
+      <c r="A38" s="65" t="s">
+        <v>56</v>
       </c>
       <c r="B38" s="27" t="s">
         <v>12</v>
@@ -6708,7 +6273,7 @@
         <v>15</v>
       </c>
       <c r="D38" s="27" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E38" s="16" t="s">
         <v>15</v>
@@ -6722,21 +6287,21 @@
       <c r="H38" s="17"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="59"/>
+      <c r="A39" s="66"/>
       <c r="B39" s="28" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D39" s="28" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E39" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F39" s="28" t="s">
         <v>58</v>
-      </c>
-      <c r="F39" s="28" t="s">
-        <v>56</v>
       </c>
       <c r="G39" s="28" t="s">
         <v>13</v>
@@ -6744,7 +6309,7 @@
       <c r="H39" s="21"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="59"/>
+      <c r="A40" s="66"/>
       <c r="B40" s="28"/>
       <c r="C40" s="1"/>
       <c r="D40" s="2" t="s">
@@ -6758,25 +6323,25 @@
       <c r="H40" s="21"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="59"/>
+      <c r="A41" s="66"/>
       <c r="B41" s="28"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E41" s="1"/>
       <c r="F41" s="28"/>
       <c r="G41" s="28" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H41" s="21"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="59"/>
+      <c r="A42" s="66"/>
       <c r="B42" s="28"/>
       <c r="C42" s="1"/>
       <c r="D42" s="30" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E42" s="1"/>
       <c r="F42" s="28"/>
@@ -6784,11 +6349,11 @@
       <c r="H42" s="21"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="59"/>
+      <c r="A43" s="66"/>
       <c r="B43" s="28"/>
       <c r="C43" s="1"/>
       <c r="D43" s="28" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="28"/>
@@ -6796,11 +6361,11 @@
       <c r="H43" s="21"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="59"/>
+      <c r="A44" s="66"/>
       <c r="B44" s="28"/>
       <c r="C44" s="1"/>
       <c r="D44" s="46" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="28"/>
@@ -6808,11 +6373,11 @@
       <c r="H44" s="21"/>
     </row>
     <row r="45" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="60"/>
+      <c r="A45" s="67"/>
       <c r="B45" s="29"/>
       <c r="C45" s="19"/>
       <c r="D45" s="47" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E45" s="19"/>
       <c r="F45" s="29"/>
@@ -6820,8 +6385,8 @@
       <c r="H45" s="20"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="58" t="s">
-        <v>64</v>
+      <c r="A46" s="65" t="s">
+        <v>66</v>
       </c>
       <c r="B46" s="16"/>
       <c r="C46" s="16"/>
@@ -6836,11 +6401,11 @@
       <c r="H46" s="17"/>
     </row>
     <row r="47" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="60"/>
+      <c r="A47" s="67"/>
       <c r="B47" s="19"/>
       <c r="C47" s="19"/>
       <c r="D47" s="19" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E47" s="19" t="s">
         <v>16</v>
@@ -6850,69 +6415,69 @@
       <c r="H47" s="20"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="58" t="s">
-        <v>118</v>
+      <c r="A48" s="65" t="s">
+        <v>120</v>
       </c>
       <c r="B48" s="16"/>
       <c r="C48" s="16"/>
       <c r="D48" s="27" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E48" s="16"/>
       <c r="F48" s="16"/>
       <c r="G48" s="35" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H48" s="17"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="59"/>
+      <c r="A49" s="66"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="28" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="36" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H49" s="21"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="59"/>
+      <c r="A50" s="66"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="30" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
       <c r="G50" s="33" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H50" s="21"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="59"/>
+      <c r="A51" s="66"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="28" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="36" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H51" s="21"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="59"/>
+      <c r="A52" s="66"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
@@ -6920,11 +6485,11 @@
       <c r="H52" s="21"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="59"/>
+      <c r="A53" s="66"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
@@ -6932,11 +6497,11 @@
       <c r="H53" s="21"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="59"/>
+      <c r="A54" s="66"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
@@ -6944,11 +6509,11 @@
       <c r="H54" s="21"/>
     </row>
     <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="60"/>
+      <c r="A55" s="67"/>
       <c r="B55" s="19"/>
       <c r="C55" s="19"/>
       <c r="D55" s="19" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E55" s="19"/>
       <c r="F55" s="19"/>
@@ -6957,43 +6522,43 @@
     </row>
     <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="B56" s="55"/>
-      <c r="C56" s="56"/>
-      <c r="D56" s="56"/>
-      <c r="E56" s="56"/>
-      <c r="F56" s="56"/>
-      <c r="G56" s="56"/>
-      <c r="H56" s="57"/>
+        <v>73</v>
+      </c>
+      <c r="B56" s="62"/>
+      <c r="C56" s="63"/>
+      <c r="D56" s="63"/>
+      <c r="E56" s="63"/>
+      <c r="F56" s="63"/>
+      <c r="G56" s="63"/>
+      <c r="H56" s="64"/>
     </row>
     <row r="57" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="B57" s="52"/>
-      <c r="C57" s="53"/>
-      <c r="D57" s="53"/>
-      <c r="E57" s="53"/>
-      <c r="F57" s="53"/>
-      <c r="G57" s="53"/>
-      <c r="H57" s="54"/>
+        <v>74</v>
+      </c>
+      <c r="B57" s="59"/>
+      <c r="C57" s="60"/>
+      <c r="D57" s="60"/>
+      <c r="E57" s="60"/>
+      <c r="F57" s="60"/>
+      <c r="G57" s="60"/>
+      <c r="H57" s="61"/>
     </row>
     <row r="58" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="B58" s="52"/>
-      <c r="C58" s="53"/>
-      <c r="D58" s="53"/>
-      <c r="E58" s="53"/>
-      <c r="F58" s="53"/>
-      <c r="G58" s="53"/>
-      <c r="H58" s="54"/>
+        <v>75</v>
+      </c>
+      <c r="B58" s="59"/>
+      <c r="C58" s="60"/>
+      <c r="D58" s="60"/>
+      <c r="E58" s="60"/>
+      <c r="F58" s="60"/>
+      <c r="G58" s="60"/>
+      <c r="H58" s="61"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="58" t="s">
-        <v>74</v>
+      <c r="A59" s="65" t="s">
+        <v>76</v>
       </c>
       <c r="B59" s="16"/>
       <c r="C59" s="16"/>
@@ -7006,29 +6571,29 @@
       <c r="H59" s="17"/>
     </row>
     <row r="60" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="60"/>
+      <c r="A60" s="67"/>
       <c r="B60" s="19"/>
       <c r="C60" s="19"/>
       <c r="D60" s="19"/>
       <c r="E60" s="19"/>
       <c r="F60" s="29" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G60" s="19"/>
       <c r="H60" s="20"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="58" t="s">
-        <v>75</v>
+      <c r="A61" s="65" t="s">
+        <v>77</v>
       </c>
       <c r="B61" s="48" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C61" s="48" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D61" s="48" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E61" s="16"/>
       <c r="F61" s="16"/>
@@ -7036,15 +6601,15 @@
       <c r="H61" s="17"/>
     </row>
     <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="60"/>
+      <c r="A62" s="67"/>
       <c r="B62" s="47" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C62" s="47" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D62" s="47" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E62" s="19"/>
       <c r="F62" s="19"/>
@@ -7052,8 +6617,8 @@
       <c r="H62" s="20"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="58" t="s">
-        <v>78</v>
+      <c r="A63" s="65" t="s">
+        <v>80</v>
       </c>
       <c r="B63" s="16"/>
       <c r="C63" s="16"/>
@@ -7061,28 +6626,28 @@
       <c r="E63" s="16"/>
       <c r="F63" s="16"/>
       <c r="G63" s="35" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H63" s="17" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="59"/>
+      <c r="A64" s="66"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="36" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H64" s="21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="59"/>
+      <c r="A65" s="66"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
@@ -7090,11 +6655,11 @@
       <c r="F65" s="1"/>
       <c r="G65" s="36"/>
       <c r="H65" s="40" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="59"/>
+      <c r="A66" s="66"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
@@ -7102,11 +6667,11 @@
       <c r="F66" s="1"/>
       <c r="G66" s="36"/>
       <c r="H66" s="38" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="59"/>
+      <c r="A67" s="66"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
@@ -7118,7 +6683,7 @@
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="59"/>
+      <c r="A68" s="66"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
@@ -7126,11 +6691,11 @@
       <c r="F68" s="1"/>
       <c r="G68" s="36"/>
       <c r="H68" s="21" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="59"/>
+      <c r="A69" s="66"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
@@ -7138,11 +6703,11 @@
       <c r="F69" s="1"/>
       <c r="G69" s="36"/>
       <c r="H69" s="40" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="60"/>
+      <c r="A70" s="67"/>
       <c r="B70" s="19"/>
       <c r="C70" s="19"/>
       <c r="D70" s="19"/>
@@ -7150,12 +6715,12 @@
       <c r="F70" s="19"/>
       <c r="G70" s="34"/>
       <c r="H70" s="39" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="58" t="s">
-        <v>85</v>
+      <c r="A71" s="65" t="s">
+        <v>87</v>
       </c>
       <c r="B71" s="16"/>
       <c r="C71" s="48" t="s">
@@ -7168,10 +6733,10 @@
       <c r="H71" s="17"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="59"/>
+      <c r="A72" s="66"/>
       <c r="B72" s="1"/>
       <c r="C72" s="49" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
@@ -7180,10 +6745,10 @@
       <c r="H72" s="21"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="59"/>
+      <c r="A73" s="66"/>
       <c r="B73" s="1"/>
       <c r="C73" s="46" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
@@ -7192,10 +6757,10 @@
       <c r="H73" s="21"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="59"/>
+      <c r="A74" s="66"/>
       <c r="B74" s="1"/>
       <c r="C74" s="49" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
@@ -7204,7 +6769,7 @@
       <c r="H74" s="21"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="59"/>
+      <c r="A75" s="66"/>
       <c r="B75" s="1"/>
       <c r="C75" s="46" t="s">
         <v>22</v>
@@ -7216,10 +6781,10 @@
       <c r="H75" s="21"/>
     </row>
     <row r="76" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="60"/>
+      <c r="A76" s="67"/>
       <c r="B76" s="19"/>
       <c r="C76" s="47" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D76" s="19"/>
       <c r="E76" s="19"/>
@@ -7228,8 +6793,8 @@
       <c r="H76" s="20"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="58" t="s">
-        <v>88</v>
+      <c r="A77" s="65" t="s">
+        <v>90</v>
       </c>
       <c r="B77" s="16"/>
       <c r="C77" s="27" t="s">
@@ -7241,29 +6806,29 @@
         <v>12</v>
       </c>
       <c r="G77" s="33" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H77" s="17"/>
     </row>
     <row r="78" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="62"/>
+      <c r="A78" s="69"/>
       <c r="B78" s="1"/>
       <c r="C78" s="28" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
       <c r="F78" s="28" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G78" s="34" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H78" s="21"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="58" t="s">
-        <v>89</v>
+      <c r="A79" s="65" t="s">
+        <v>91</v>
       </c>
       <c r="B79" s="25"/>
       <c r="C79" s="25"/>
@@ -7272,7 +6837,7 @@
       </c>
       <c r="E79" s="16"/>
       <c r="F79" s="43" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G79" s="16" t="s">
         <v>15</v>
@@ -7282,25 +6847,25 @@
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="59"/>
+      <c r="A80" s="66"/>
       <c r="B80" s="12"/>
       <c r="C80" s="12"/>
       <c r="D80" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E80" s="1"/>
       <c r="F80" s="44" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="H80" s="50" t="s">
-        <v>137</v>
+        <v>95</v>
+      </c>
+      <c r="H80" s="56" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="59"/>
+      <c r="A81" s="66"/>
       <c r="B81" s="12"/>
       <c r="C81" s="12"/>
       <c r="D81" s="1"/>
@@ -7312,34 +6877,34 @@
       <c r="H81" s="21"/>
     </row>
     <row r="82" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="60"/>
+      <c r="A82" s="67"/>
       <c r="B82" s="26"/>
       <c r="C82" s="26"/>
       <c r="D82" s="19"/>
       <c r="E82" s="19"/>
       <c r="F82" s="19" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G82" s="19"/>
       <c r="H82" s="20"/>
     </row>
     <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="14" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B83" s="16"/>
-      <c r="C83" s="52" t="s">
+      <c r="C83" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D83" s="53"/>
-      <c r="E83" s="53"/>
-      <c r="F83" s="53"/>
-      <c r="G83" s="53"/>
-      <c r="H83" s="54"/>
+      <c r="D83" s="60"/>
+      <c r="E83" s="60"/>
+      <c r="F83" s="60"/>
+      <c r="G83" s="60"/>
+      <c r="H83" s="61"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="58" t="s">
-        <v>96</v>
+      <c r="A84" s="65" t="s">
+        <v>98</v>
       </c>
       <c r="B84" s="16"/>
       <c r="C84" s="16"/>
@@ -7352,11 +6917,11 @@
       <c r="H84" s="17"/>
     </row>
     <row r="85" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="62"/>
+      <c r="A85" s="69"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
       <c r="D85" s="28" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
@@ -7365,31 +6930,31 @@
     </row>
     <row r="86" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="22" t="s">
-        <v>97</v>
-      </c>
-      <c r="B86" s="52"/>
-      <c r="C86" s="53"/>
-      <c r="D86" s="53"/>
-      <c r="E86" s="53"/>
-      <c r="F86" s="53"/>
-      <c r="G86" s="53"/>
-      <c r="H86" s="54"/>
+        <v>99</v>
+      </c>
+      <c r="B86" s="59"/>
+      <c r="C86" s="60"/>
+      <c r="D86" s="60"/>
+      <c r="E86" s="60"/>
+      <c r="F86" s="60"/>
+      <c r="G86" s="60"/>
+      <c r="H86" s="61"/>
     </row>
     <row r="87" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="B87" s="52"/>
-      <c r="C87" s="53"/>
-      <c r="D87" s="53"/>
-      <c r="E87" s="53"/>
-      <c r="F87" s="53"/>
-      <c r="G87" s="53"/>
-      <c r="H87" s="54"/>
+        <v>100</v>
+      </c>
+      <c r="B87" s="59"/>
+      <c r="C87" s="60"/>
+      <c r="D87" s="60"/>
+      <c r="E87" s="60"/>
+      <c r="F87" s="60"/>
+      <c r="G87" s="60"/>
+      <c r="H87" s="61"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="58" t="s">
-        <v>99</v>
+      <c r="A88" s="65" t="s">
+        <v>101</v>
       </c>
       <c r="B88" s="16"/>
       <c r="C88" s="16" t="s">
@@ -7401,17 +6966,17 @@
         <v>15</v>
       </c>
       <c r="G88" s="35" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H88" s="37" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="59"/>
+      <c r="A89" s="66"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D89" s="1"/>
       <c r="E89" s="1"/>
@@ -7419,14 +6984,14 @@
         <v>26</v>
       </c>
       <c r="G89" s="36" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H89" s="38" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="59"/>
+      <c r="A90" s="66"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
       <c r="D90" s="1"/>
@@ -7440,22 +7005,22 @@
       </c>
     </row>
     <row r="91" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="60"/>
+      <c r="A91" s="67"/>
       <c r="B91" s="19"/>
       <c r="C91" s="19"/>
       <c r="D91" s="19"/>
       <c r="E91" s="19"/>
       <c r="F91" s="19"/>
       <c r="G91" s="19" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H91" s="20" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="58" t="s">
-        <v>101</v>
+      <c r="A92" s="65" t="s">
+        <v>103</v>
       </c>
       <c r="B92" s="16"/>
       <c r="C92" s="16"/>
@@ -7465,30 +7030,30 @@
       <c r="E92" s="16"/>
       <c r="F92" s="16"/>
       <c r="G92" s="27" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H92" s="37" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="59"/>
+      <c r="A93" s="66"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
       <c r="D93" s="28" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E93" s="1"/>
       <c r="F93" s="1"/>
       <c r="G93" s="28" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H93" s="38" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="59"/>
+      <c r="A94" s="66"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
       <c r="D94" s="28"/>
@@ -7497,52 +7062,52 @@
       <c r="G94" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="H94" s="66"/>
+      <c r="H94" s="73"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="59"/>
+      <c r="A95" s="66"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
       <c r="D95" s="28"/>
       <c r="E95" s="1"/>
       <c r="F95" s="1"/>
       <c r="G95" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="H95" s="66"/>
+        <v>59</v>
+      </c>
+      <c r="H95" s="73"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A96" s="59"/>
+      <c r="A96" s="66"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
       <c r="D96" s="28"/>
       <c r="E96" s="1"/>
       <c r="F96" s="1"/>
       <c r="G96" s="33" t="s">
-        <v>79</v>
-      </c>
-      <c r="H96" s="66"/>
+        <v>81</v>
+      </c>
+      <c r="H96" s="73"/>
     </row>
     <row r="97" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="60"/>
+      <c r="A97" s="67"/>
       <c r="B97" s="19"/>
       <c r="C97" s="19"/>
       <c r="D97" s="29"/>
       <c r="E97" s="19"/>
       <c r="F97" s="19"/>
       <c r="G97" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="H97" s="67"/>
+        <v>105</v>
+      </c>
+      <c r="H97" s="74"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B98" s="61"/>
-      <c r="C98" s="61"/>
-      <c r="D98" s="61"/>
-      <c r="E98" s="61"/>
-      <c r="F98" s="61"/>
-      <c r="G98" s="61"/>
-      <c r="H98" s="61"/>
+      <c r="B98" s="68"/>
+      <c r="C98" s="68"/>
+      <c r="D98" s="68"/>
+      <c r="E98" s="68"/>
+      <c r="F98" s="68"/>
+      <c r="G98" s="68"/>
+      <c r="H98" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -7594,36 +7159,36 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="64" t="s">
-        <v>104</v>
-      </c>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
+      <c r="B4" s="71" t="s">
+        <v>106</v>
+      </c>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="65" t="s">
-        <v>105</v>
-      </c>
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="65"/>
+      <c r="B5" s="72" t="s">
+        <v>107</v>
+      </c>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -7730,7 +7295,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B13" s="7">
         <v>0</v>
@@ -7747,7 +7312,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B14" s="7">
         <v>0</v>
@@ -7764,7 +7329,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B15" s="7">
         <v>0</v>
@@ -7781,7 +7346,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B16" s="7">
         <v>0</v>
@@ -7798,7 +7363,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B17" s="7">
         <v>0</v>
@@ -7815,7 +7380,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B18" s="7">
         <v>0</v>
@@ -7832,7 +7397,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B19" s="7">
         <v>0</v>
@@ -7849,7 +7414,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B20" s="7">
         <v>0</v>
@@ -7866,7 +7431,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B21" s="7">
         <v>0</v>
@@ -7883,7 +7448,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B22" s="7">
         <v>0</v>
@@ -7900,7 +7465,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B23" s="7">
         <v>0</v>
@@ -7917,7 +7482,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B24" s="7">
         <v>0</v>
@@ -7934,7 +7499,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B25" s="7">
         <v>0</v>
@@ -7951,7 +7516,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B26" s="7">
         <v>0</v>
@@ -7968,7 +7533,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B27" s="7">
         <v>0</v>
@@ -7985,7 +7550,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B28" s="7">
         <v>0</v>
@@ -8002,7 +7567,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B29" s="7">
         <v>0</v>
@@ -8019,7 +7584,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B30" s="7">
         <v>0</v>
@@ -8036,7 +7601,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B31" s="7">
         <v>0</v>
@@ -8053,7 +7618,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B32" s="7">
         <v>0</v>
@@ -8070,7 +7635,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B33" s="7">
         <v>0</v>
@@ -8120,40 +7685,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/Plannings 2026 S25 v2.xlsx
+++ b/Plannings 2026 S25 v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{7AA5A74F-8B5F-4333-8824-7AED61442DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71C3B252-B6E7-4AF0-9872-A5BAA55BFE97}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{7AA5A74F-8B5F-4333-8824-7AED61442DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7C578E8-5856-41AB-A6B4-F34072F8A9CE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -883,7 +883,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1094,6 +1094,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6140,8 +6143,8 @@
       <c r="G2" s="63"/>
       <c r="H2" s="63"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="13" t="s">
+    <row r="3" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="71" t="s">
         <v>130</v>
       </c>
       <c r="C3" s="13" t="s">

--- a/Plannings 2026 S25 v2.xlsx
+++ b/Plannings 2026 S25 v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{7AA5A74F-8B5F-4333-8824-7AED61442DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7C578E8-5856-41AB-A6B4-F34072F8A9CE}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{7AA5A74F-8B5F-4333-8824-7AED61442DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91543A58-BBC7-41CA-8B14-C6BE072B0216}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="142">
   <si>
     <t>Planning des salariés du 15/06/2026 au 21/06/2026</t>
   </si>
@@ -445,6 +445,9 @@
   </si>
   <si>
     <t>11:00/14:30</t>
+  </si>
+  <si>
+    <t>Commercial : reconduction EDF</t>
   </si>
 </sst>
 </file>
@@ -602,7 +605,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -879,11 +882,48 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1098,6 +1138,15 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1127,13 +1176,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1171,13 +1220,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1215,13 +1264,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1259,13 +1308,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1303,13 +1352,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1347,13 +1396,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1391,13 +1440,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1435,13 +1484,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1479,13 +1528,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1523,13 +1572,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1567,13 +1616,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1611,13 +1660,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1655,13 +1704,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1699,13 +1748,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1743,13 +1792,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1787,13 +1836,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1831,13 +1880,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1875,13 +1924,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1919,13 +1968,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1963,13 +2012,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2007,13 +2056,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2051,13 +2100,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2095,13 +2144,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2139,13 +2188,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2183,13 +2232,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2227,13 +2276,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2271,13 +2320,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2315,13 +2364,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2359,13 +2408,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2403,13 +2452,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2447,13 +2496,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2491,13 +2540,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2535,13 +2584,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2579,13 +2628,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2623,13 +2672,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2667,13 +2716,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2711,13 +2760,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2755,13 +2804,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2799,13 +2848,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2843,13 +2892,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2887,13 +2936,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2931,13 +2980,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2975,13 +3024,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3019,13 +3068,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3063,13 +3112,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3107,13 +3156,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3151,13 +3200,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3195,13 +3244,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3239,13 +3288,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>53</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>53</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3283,13 +3332,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3327,13 +3376,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3371,13 +3420,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>59</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>59</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3415,13 +3464,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>61</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>61</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3459,13 +3508,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>61</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>61</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3503,13 +3552,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>61</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>61</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3547,13 +3596,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>63</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>63</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3591,13 +3640,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>63</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>63</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3635,13 +3684,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3679,13 +3728,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>67</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>67</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3723,13 +3772,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>69</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>69</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3767,13 +3816,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3811,13 +3860,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>73</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>73</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3855,13 +3904,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3899,13 +3948,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3943,13 +3992,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3987,13 +4036,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>79</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>79</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4031,13 +4080,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>79</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>79</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4075,13 +4124,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>81</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>81</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4119,13 +4168,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>79</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>79</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4163,13 +4212,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>79</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>79</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4207,13 +4256,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
+      <xdr:row>84</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>83</xdr:row>
+      <xdr:row>84</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4251,13 +4300,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>88</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>88</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4295,13 +4344,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>88</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>88</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4339,13 +4388,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>88</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>88</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4383,13 +4432,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>89</xdr:row>
+      <xdr:row>90</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>89</xdr:row>
+      <xdr:row>90</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4427,13 +4476,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>88</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>88</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4471,13 +4520,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>91</xdr:row>
+      <xdr:row>92</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>91</xdr:row>
+      <xdr:row>92</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4515,13 +4564,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>91</xdr:row>
+      <xdr:row>92</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>91</xdr:row>
+      <xdr:row>92</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4559,13 +4608,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>93</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>93</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4603,13 +4652,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>95</xdr:row>
+      <xdr:row>96</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>95</xdr:row>
+      <xdr:row>96</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4647,13 +4696,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4691,13 +4740,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4735,13 +4784,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4779,13 +4828,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4823,13 +4872,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4867,13 +4916,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4911,13 +4960,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4955,13 +5004,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4999,13 +5048,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5043,13 +5092,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5087,13 +5136,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5131,13 +5180,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5175,13 +5224,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>89</xdr:row>
+      <xdr:row>90</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>89</xdr:row>
+      <xdr:row>90</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5219,13 +5268,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5263,13 +5312,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>91</xdr:row>
+      <xdr:row>92</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>91</xdr:row>
+      <xdr:row>92</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5307,13 +5356,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5351,13 +5400,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5395,13 +5444,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5439,13 +5488,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5483,13 +5532,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5527,13 +5576,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5571,13 +5620,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5615,13 +5664,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5659,13 +5708,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5703,13 +5752,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6115,7 +6164,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H98"/>
+  <dimension ref="A1:H99"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="52.42578125" customWidth="1"/>
@@ -6143,275 +6192,272 @@
       <c r="G2" s="63"/>
       <c r="H2" s="63"/>
     </row>
-    <row r="3" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="71" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B3" s="72" t="s">
+        <v>141</v>
+      </c>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="74"/>
+    </row>
+    <row r="4" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="71" t="s">
         <v>130</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C4" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D4" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E4" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F4" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G4" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H4" s="13" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
+    <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B5" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C5" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D5" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E5" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F5" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H5" s="13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="58" t="s">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="27" t="s">
+      <c r="B6" s="15"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="17"/>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="60"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="29" t="s">
+      <c r="H6" s="17"/>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="60"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="20"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="58" t="s">
+      <c r="H7" s="20"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16" t="s">
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="17"/>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="60"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19" t="s">
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="17"/>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="60"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="20"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="58" t="s">
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="20"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="58" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="31" t="s">
+      <c r="B10" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16" t="s">
+      <c r="C10" s="16"/>
+      <c r="D10" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E10" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="17"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="59"/>
-      <c r="B10" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="21"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="17"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="59"/>
-      <c r="B11" s="2" t="s">
-        <v>15</v>
+      <c r="B11" s="32" t="s">
+        <v>19</v>
       </c>
       <c r="C11" s="1"/>
-      <c r="D11" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="1"/>
+      <c r="D11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="21"/>
     </row>
-    <row r="12" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="60"/>
-      <c r="B12" s="19" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="59"/>
+      <c r="B12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="21"/>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="60"/>
+      <c r="B13" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="47" t="s">
+      <c r="C13" s="19"/>
+      <c r="D13" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="20"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="58" t="s">
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="20"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B14" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="17"/>
-    </row>
-    <row r="14" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="60"/>
-      <c r="B14" s="19" t="s">
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="17"/>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="60"/>
+      <c r="B15" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="20"/>
-    </row>
-    <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="22" t="s">
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="20"/>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="52"/>
-      <c r="C15" s="53"/>
-      <c r="D15" s="53"/>
-      <c r="E15" s="53"/>
-      <c r="F15" s="53"/>
-      <c r="G15" s="53"/>
-      <c r="H15" s="54"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="68" t="s">
+      <c r="B16" s="52"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="53"/>
+      <c r="H16" s="54"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G17" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="H16" s="1"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="68"/>
-      <c r="B17" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>140</v>
       </c>
       <c r="H17" s="1"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="68"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="69" t="s">
-        <v>127</v>
-      </c>
-      <c r="D18" s="69" t="s">
-        <v>127</v>
-      </c>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
+      <c r="B18" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>140</v>
+      </c>
       <c r="H18" s="1"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="68"/>
       <c r="B19" s="1"/>
-      <c r="C19" s="70" t="s">
-        <v>128</v>
-      </c>
-      <c r="D19" s="70" t="s">
-        <v>128</v>
+      <c r="C19" s="69" t="s">
+        <v>127</v>
+      </c>
+      <c r="D19" s="69" t="s">
+        <v>127</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
@@ -6421,152 +6467,148 @@
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="68"/>
       <c r="B20" s="1"/>
-      <c r="C20" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>15</v>
+      <c r="C20" s="70" t="s">
+        <v>128</v>
+      </c>
+      <c r="D20" s="70" t="s">
+        <v>128</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="68"/>
       <c r="B21" s="1"/>
-      <c r="C21" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>129</v>
+      <c r="C21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="58" t="s">
+    <row r="22" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="68"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B23" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C23" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16" t="s">
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="G22" s="35" t="s">
+      <c r="G23" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="H22" s="37" t="s">
+      <c r="H23" s="37" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="59"/>
-      <c r="B23" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G23" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="H23" s="41" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="59"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
+      <c r="B24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="2" t="s">
+      <c r="F24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G24" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="H24" s="41" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="59"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H24" s="42" t="s">
+      <c r="H25" s="42" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="60"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19" t="s">
+    <row r="26" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="60"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="H25" s="51" t="s">
+      <c r="H26" s="51" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="58" t="s">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="58" t="s">
         <v>34</v>
       </c>
-      <c r="B26" s="43" t="s">
+      <c r="B27" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="27" t="s">
+      <c r="C27" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="D26" s="27" t="s">
+      <c r="D27" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="E26" s="27" t="s">
+      <c r="E27" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="17"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="59"/>
-      <c r="B27" s="44" t="s">
-        <v>37</v>
-      </c>
-      <c r="C27" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="D27" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="E27" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="21"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="17"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="59"/>
-      <c r="B28" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="C28" s="45" t="s">
-        <v>42</v>
-      </c>
-      <c r="D28" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>15</v>
+      <c r="B28" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="D28" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="E28" s="28" t="s">
+        <v>40</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
@@ -6574,17 +6616,17 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="59"/>
-      <c r="B29" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="C29" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="D29" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>46</v>
+      <c r="B29" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="D29" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
@@ -6592,14 +6634,18 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="59"/>
-      <c r="B30" s="28"/>
-      <c r="C30" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E30" s="1"/>
+      <c r="B30" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="D30" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="21"/>
@@ -6607,11 +6653,11 @@
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="59"/>
       <c r="B31" s="28"/>
-      <c r="C31" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>49</v>
+      <c r="C31" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
@@ -6621,11 +6667,11 @@
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="59"/>
       <c r="B32" s="28"/>
-      <c r="C32" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D32" s="30" t="s">
-        <v>36</v>
+      <c r="C32" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
@@ -6635,11 +6681,11 @@
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="59"/>
       <c r="B33" s="28"/>
-      <c r="C33" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D33" s="28" t="s">
-        <v>51</v>
+      <c r="C33" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D33" s="30" t="s">
+        <v>36</v>
       </c>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
@@ -6649,20 +6695,22 @@
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="59"/>
       <c r="B34" s="28"/>
-      <c r="C34" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="D34" s="28"/>
+      <c r="C34" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D34" s="28" t="s">
+        <v>51</v>
+      </c>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
       <c r="H34" s="21"/>
     </row>
-    <row r="35" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="62"/>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="59"/>
       <c r="B35" s="28"/>
-      <c r="C35" s="28" t="s">
-        <v>52</v>
+      <c r="C35" s="30" t="s">
+        <v>36</v>
       </c>
       <c r="D35" s="28"/>
       <c r="E35" s="1"/>
@@ -6670,93 +6718,91 @@
       <c r="G35" s="1"/>
       <c r="H35" s="21"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="58" t="s">
+    <row r="36" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="62"/>
+      <c r="B36" s="28"/>
+      <c r="C36" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="D36" s="28"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="21"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="B36" s="16"/>
-      <c r="C36" s="16"/>
-      <c r="D36" s="27" t="s">
+      <c r="B37" s="16"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="27" t="s">
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="H36" s="17"/>
-    </row>
-    <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="60"/>
-      <c r="B37" s="19"/>
-      <c r="C37" s="19"/>
-      <c r="D37" s="29" t="s">
+      <c r="H37" s="17"/>
+    </row>
+    <row r="38" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="60"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="29" t="s">
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="H37" s="20"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="58" t="s">
+      <c r="H38" s="20"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="B38" s="27" t="s">
+      <c r="B39" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="C38" s="16" t="s">
+      <c r="C39" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="D38" s="27" t="s">
+      <c r="D39" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="E38" s="16" t="s">
+      <c r="E39" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="F38" s="27" t="s">
+      <c r="F39" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="G38" s="27" t="s">
+      <c r="G39" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="H38" s="17"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="59"/>
-      <c r="B39" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D39" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F39" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="G39" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="H39" s="21"/>
+      <c r="H39" s="17"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="59"/>
-      <c r="B40" s="28"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E40" s="1"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="30" t="s">
-        <v>12</v>
+      <c r="B40" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D40" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F40" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="G40" s="28" t="s">
+        <v>13</v>
       </c>
       <c r="H40" s="21"/>
     </row>
@@ -6764,13 +6810,13 @@
       <c r="A41" s="59"/>
       <c r="B41" s="28"/>
       <c r="C41" s="1"/>
-      <c r="D41" s="1" t="s">
-        <v>59</v>
+      <c r="D41" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="E41" s="1"/>
       <c r="F41" s="28"/>
-      <c r="G41" s="28" t="s">
-        <v>60</v>
+      <c r="G41" s="30" t="s">
+        <v>12</v>
       </c>
       <c r="H41" s="21"/>
     </row>
@@ -6778,20 +6824,22 @@
       <c r="A42" s="59"/>
       <c r="B42" s="28"/>
       <c r="C42" s="1"/>
-      <c r="D42" s="30" t="s">
-        <v>55</v>
+      <c r="D42" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="E42" s="1"/>
       <c r="F42" s="28"/>
-      <c r="G42" s="28"/>
+      <c r="G42" s="28" t="s">
+        <v>60</v>
+      </c>
       <c r="H42" s="21"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="59"/>
       <c r="B43" s="28"/>
       <c r="C43" s="1"/>
-      <c r="D43" s="28" t="s">
-        <v>61</v>
+      <c r="D43" s="30" t="s">
+        <v>55</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="28"/>
@@ -6802,97 +6850,95 @@
       <c r="A44" s="59"/>
       <c r="B44" s="28"/>
       <c r="C44" s="1"/>
-      <c r="D44" s="46" t="s">
-        <v>62</v>
+      <c r="D44" s="28" t="s">
+        <v>61</v>
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="28"/>
       <c r="G44" s="28"/>
       <c r="H44" s="21"/>
     </row>
-    <row r="45" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="60"/>
-      <c r="B45" s="29"/>
-      <c r="C45" s="19"/>
-      <c r="D45" s="47" t="s">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="59"/>
+      <c r="B45" s="28"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="46" t="s">
+        <v>62</v>
+      </c>
+      <c r="E45" s="1"/>
+      <c r="F45" s="28"/>
+      <c r="G45" s="28"/>
+      <c r="H45" s="21"/>
+    </row>
+    <row r="46" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="60"/>
+      <c r="B46" s="29"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="E45" s="19"/>
-      <c r="F45" s="29"/>
-      <c r="G45" s="29"/>
-      <c r="H45" s="20"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="58" t="s">
+      <c r="E46" s="19"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="29"/>
+      <c r="H46" s="20"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="58" t="s">
         <v>64</v>
       </c>
-      <c r="B46" s="16"/>
-      <c r="C46" s="16"/>
-      <c r="D46" s="16" t="s">
+      <c r="B47" s="16"/>
+      <c r="C47" s="16"/>
+      <c r="D47" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="E46" s="16" t="s">
+      <c r="E47" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="F46" s="16"/>
-      <c r="G46" s="16"/>
-      <c r="H46" s="17"/>
-    </row>
-    <row r="47" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="60"/>
-      <c r="B47" s="19"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="19" t="s">
+      <c r="F47" s="16"/>
+      <c r="G47" s="16"/>
+      <c r="H47" s="17"/>
+    </row>
+    <row r="48" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="60"/>
+      <c r="B48" s="19"/>
+      <c r="C48" s="19"/>
+      <c r="D48" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="E47" s="19" t="s">
+      <c r="E48" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F47" s="19"/>
-      <c r="G47" s="19"/>
-      <c r="H47" s="20"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="58" t="s">
+      <c r="F48" s="19"/>
+      <c r="G48" s="19"/>
+      <c r="H48" s="20"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="58" t="s">
         <v>118</v>
       </c>
-      <c r="B48" s="16"/>
-      <c r="C48" s="16"/>
-      <c r="D48" s="27" t="s">
+      <c r="B49" s="16"/>
+      <c r="C49" s="16"/>
+      <c r="D49" s="27" t="s">
         <v>120</v>
       </c>
-      <c r="E48" s="16"/>
-      <c r="F48" s="16"/>
-      <c r="G48" s="35" t="s">
+      <c r="E49" s="16"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="35" t="s">
         <v>123</v>
       </c>
-      <c r="H48" s="17"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="59"/>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-      <c r="D49" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
-      <c r="G49" s="36" t="s">
-        <v>67</v>
-      </c>
-      <c r="H49" s="21"/>
+      <c r="H49" s="17"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="59"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
-      <c r="D50" s="30" t="s">
-        <v>119</v>
+      <c r="D50" s="28" t="s">
+        <v>67</v>
       </c>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
-      <c r="G50" s="33" t="s">
-        <v>124</v>
+      <c r="G50" s="36" t="s">
+        <v>67</v>
       </c>
       <c r="H50" s="21"/>
     </row>
@@ -6900,13 +6946,13 @@
       <c r="A51" s="59"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
-      <c r="D51" s="28" t="s">
-        <v>68</v>
+      <c r="D51" s="30" t="s">
+        <v>119</v>
       </c>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
-      <c r="G51" s="36" t="s">
-        <v>68</v>
+      <c r="G51" s="33" t="s">
+        <v>124</v>
       </c>
       <c r="H51" s="21"/>
     </row>
@@ -6914,20 +6960,22 @@
       <c r="A52" s="59"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
-      <c r="D52" s="2" t="s">
-        <v>121</v>
+      <c r="D52" s="28" t="s">
+        <v>68</v>
       </c>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
-      <c r="G52" s="36"/>
+      <c r="G52" s="36" t="s">
+        <v>68</v>
+      </c>
       <c r="H52" s="21"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="59"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
-      <c r="D53" s="1" t="s">
-        <v>69</v>
+      <c r="D53" s="2" t="s">
+        <v>121</v>
       </c>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
@@ -6938,53 +6986,53 @@
       <c r="A54" s="59"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
-      <c r="D54" s="2" t="s">
-        <v>122</v>
+      <c r="D54" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="36"/>
       <c r="H54" s="21"/>
     </row>
-    <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="60"/>
-      <c r="B55" s="19"/>
-      <c r="C55" s="19"/>
-      <c r="D55" s="19" t="s">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="59"/>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="36"/>
+      <c r="H55" s="21"/>
+    </row>
+    <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="60"/>
+      <c r="B56" s="19"/>
+      <c r="C56" s="19"/>
+      <c r="D56" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="E55" s="19"/>
-      <c r="F55" s="19"/>
-      <c r="G55" s="34"/>
-      <c r="H55" s="20"/>
-    </row>
-    <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="23" t="s">
+      <c r="E56" s="19"/>
+      <c r="F56" s="19"/>
+      <c r="G56" s="34"/>
+      <c r="H56" s="20"/>
+    </row>
+    <row r="57" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="B56" s="55"/>
-      <c r="C56" s="56"/>
-      <c r="D56" s="56"/>
-      <c r="E56" s="56"/>
-      <c r="F56" s="56"/>
-      <c r="G56" s="56"/>
-      <c r="H56" s="57"/>
-    </row>
-    <row r="57" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="14" t="s">
+      <c r="B57" s="55"/>
+      <c r="C57" s="56"/>
+      <c r="D57" s="56"/>
+      <c r="E57" s="56"/>
+      <c r="F57" s="56"/>
+      <c r="G57" s="56"/>
+      <c r="H57" s="57"/>
+    </row>
+    <row r="58" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="14" t="s">
         <v>72</v>
-      </c>
-      <c r="B57" s="52"/>
-      <c r="C57" s="53"/>
-      <c r="D57" s="53"/>
-      <c r="E57" s="53"/>
-      <c r="F57" s="53"/>
-      <c r="G57" s="53"/>
-      <c r="H57" s="54"/>
-    </row>
-    <row r="58" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="22" t="s">
-        <v>73</v>
       </c>
       <c r="B58" s="52"/>
       <c r="C58" s="53"/>
@@ -6994,94 +7042,92 @@
       <c r="G58" s="53"/>
       <c r="H58" s="54"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="58" t="s">
+    <row r="59" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="B59" s="52"/>
+      <c r="C59" s="53"/>
+      <c r="D59" s="53"/>
+      <c r="E59" s="53"/>
+      <c r="F59" s="53"/>
+      <c r="G59" s="53"/>
+      <c r="H59" s="54"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="58" t="s">
         <v>74</v>
       </c>
-      <c r="B59" s="16"/>
-      <c r="C59" s="16"/>
-      <c r="D59" s="16"/>
-      <c r="E59" s="16"/>
-      <c r="F59" s="27" t="s">
+      <c r="B60" s="16"/>
+      <c r="C60" s="16"/>
+      <c r="D60" s="16"/>
+      <c r="E60" s="16"/>
+      <c r="F60" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="G59" s="16"/>
-      <c r="H59" s="17"/>
-    </row>
-    <row r="60" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="60"/>
-      <c r="B60" s="19"/>
-      <c r="C60" s="19"/>
-      <c r="D60" s="19"/>
-      <c r="E60" s="19"/>
-      <c r="F60" s="29" t="s">
+      <c r="G60" s="16"/>
+      <c r="H60" s="17"/>
+    </row>
+    <row r="61" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="60"/>
+      <c r="B61" s="19"/>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="G60" s="19"/>
-      <c r="H60" s="20"/>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="58" t="s">
+      <c r="G61" s="19"/>
+      <c r="H61" s="20"/>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="58" t="s">
         <v>75</v>
       </c>
-      <c r="B61" s="48" t="s">
+      <c r="B62" s="48" t="s">
         <v>62</v>
       </c>
-      <c r="C61" s="48" t="s">
+      <c r="C62" s="48" t="s">
         <v>62</v>
       </c>
-      <c r="D61" s="48" t="s">
+      <c r="D62" s="48" t="s">
         <v>62</v>
       </c>
-      <c r="E61" s="16"/>
-      <c r="F61" s="16"/>
-      <c r="G61" s="16"/>
-      <c r="H61" s="17"/>
-    </row>
-    <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="60"/>
-      <c r="B62" s="47" t="s">
+      <c r="E62" s="16"/>
+      <c r="F62" s="16"/>
+      <c r="G62" s="16"/>
+      <c r="H62" s="17"/>
+    </row>
+    <row r="63" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="60"/>
+      <c r="B63" s="47" t="s">
         <v>76</v>
       </c>
-      <c r="C62" s="47" t="s">
+      <c r="C63" s="47" t="s">
         <v>76</v>
       </c>
-      <c r="D62" s="47" t="s">
+      <c r="D63" s="47" t="s">
         <v>77</v>
       </c>
-      <c r="E62" s="19"/>
-      <c r="F62" s="19"/>
-      <c r="G62" s="19"/>
-      <c r="H62" s="20"/>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="58" t="s">
+      <c r="E63" s="19"/>
+      <c r="F63" s="19"/>
+      <c r="G63" s="19"/>
+      <c r="H63" s="20"/>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="58" t="s">
         <v>78</v>
       </c>
-      <c r="B63" s="16"/>
-      <c r="C63" s="16"/>
-      <c r="D63" s="16"/>
-      <c r="E63" s="16"/>
-      <c r="F63" s="16"/>
-      <c r="G63" s="35" t="s">
+      <c r="B64" s="16"/>
+      <c r="C64" s="16"/>
+      <c r="D64" s="16"/>
+      <c r="E64" s="16"/>
+      <c r="F64" s="16"/>
+      <c r="G64" s="35" t="s">
         <v>79</v>
       </c>
-      <c r="H63" s="17" t="s">
+      <c r="H64" s="17" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="59"/>
-      <c r="B64" s="1"/>
-      <c r="C64" s="1"/>
-      <c r="D64" s="1"/>
-      <c r="E64" s="1"/>
-      <c r="F64" s="1"/>
-      <c r="G64" s="36" t="s">
-        <v>125</v>
-      </c>
-      <c r="H64" s="21" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -7091,9 +7137,11 @@
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
-      <c r="G65" s="36"/>
-      <c r="H65" s="40" t="s">
-        <v>79</v>
+      <c r="G65" s="36" t="s">
+        <v>125</v>
+      </c>
+      <c r="H65" s="21" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
@@ -7104,8 +7152,8 @@
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
       <c r="G66" s="36"/>
-      <c r="H66" s="38" t="s">
-        <v>82</v>
+      <c r="H66" s="40" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -7116,8 +7164,8 @@
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
       <c r="G67" s="36"/>
-      <c r="H67" s="24" t="s">
-        <v>15</v>
+      <c r="H67" s="38" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -7128,8 +7176,8 @@
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
       <c r="G68" s="36"/>
-      <c r="H68" s="21" t="s">
-        <v>83</v>
+      <c r="H68" s="24" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -7140,53 +7188,53 @@
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
       <c r="G69" s="36"/>
-      <c r="H69" s="40" t="s">
+      <c r="H69" s="21" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="59"/>
+      <c r="B70" s="1"/>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="36"/>
+      <c r="H70" s="40" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="60"/>
-      <c r="B70" s="19"/>
-      <c r="C70" s="19"/>
-      <c r="D70" s="19"/>
-      <c r="E70" s="19"/>
-      <c r="F70" s="19"/>
-      <c r="G70" s="34"/>
-      <c r="H70" s="39" t="s">
+    <row r="71" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="60"/>
+      <c r="B71" s="19"/>
+      <c r="C71" s="19"/>
+      <c r="D71" s="19"/>
+      <c r="E71" s="19"/>
+      <c r="F71" s="19"/>
+      <c r="G71" s="34"/>
+      <c r="H71" s="39" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="58" t="s">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="58" t="s">
         <v>85</v>
       </c>
-      <c r="B71" s="16"/>
-      <c r="C71" s="48" t="s">
+      <c r="B72" s="16"/>
+      <c r="C72" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="D71" s="16"/>
-      <c r="E71" s="16"/>
-      <c r="F71" s="16"/>
-      <c r="G71" s="16"/>
-      <c r="H71" s="17"/>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="59"/>
-      <c r="B72" s="1"/>
-      <c r="C72" s="49" t="s">
-        <v>86</v>
-      </c>
-      <c r="D72" s="1"/>
-      <c r="E72" s="1"/>
-      <c r="F72" s="1"/>
-      <c r="G72" s="1"/>
-      <c r="H72" s="21"/>
+      <c r="D72" s="16"/>
+      <c r="E72" s="16"/>
+      <c r="F72" s="16"/>
+      <c r="G72" s="16"/>
+      <c r="H72" s="17"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="59"/>
       <c r="B73" s="1"/>
-      <c r="C73" s="46" t="s">
-        <v>62</v>
+      <c r="C73" s="49" t="s">
+        <v>86</v>
       </c>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
@@ -7197,8 +7245,8 @@
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="59"/>
       <c r="B74" s="1"/>
-      <c r="C74" s="49" t="s">
-        <v>63</v>
+      <c r="C74" s="46" t="s">
+        <v>62</v>
       </c>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
@@ -7209,8 +7257,8 @@
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="59"/>
       <c r="B75" s="1"/>
-      <c r="C75" s="46" t="s">
-        <v>22</v>
+      <c r="C75" s="49" t="s">
+        <v>63</v>
       </c>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
@@ -7218,169 +7266,169 @@
       <c r="G75" s="1"/>
       <c r="H75" s="21"/>
     </row>
-    <row r="76" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="60"/>
-      <c r="B76" s="19"/>
-      <c r="C76" s="47" t="s">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="59"/>
+      <c r="B76" s="1"/>
+      <c r="C76" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="21"/>
+    </row>
+    <row r="77" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="60"/>
+      <c r="B77" s="19"/>
+      <c r="C77" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="D76" s="19"/>
-      <c r="E76" s="19"/>
-      <c r="F76" s="19"/>
-      <c r="G76" s="19"/>
-      <c r="H76" s="20"/>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="58" t="s">
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="20"/>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="58" t="s">
         <v>88</v>
       </c>
-      <c r="B77" s="16"/>
-      <c r="C77" s="27" t="s">
+      <c r="B78" s="16"/>
+      <c r="C78" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="D77" s="16"/>
-      <c r="E77" s="16"/>
-      <c r="F77" s="27" t="s">
+      <c r="D78" s="16"/>
+      <c r="E78" s="16"/>
+      <c r="F78" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="G77" s="33" t="s">
+      <c r="G78" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="H77" s="17"/>
-    </row>
-    <row r="78" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="62"/>
-      <c r="B78" s="1"/>
-      <c r="C78" s="28" t="s">
+      <c r="H78" s="17"/>
+    </row>
+    <row r="79" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="62"/>
+      <c r="B79" s="1"/>
+      <c r="C79" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="D78" s="1"/>
-      <c r="E78" s="1"/>
-      <c r="F78" s="28" t="s">
+      <c r="D79" s="1"/>
+      <c r="E79" s="1"/>
+      <c r="F79" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="G78" s="34" t="s">
+      <c r="G79" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="H78" s="21"/>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="58" t="s">
+      <c r="H79" s="21"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" s="58" t="s">
         <v>89</v>
       </c>
-      <c r="B79" s="25"/>
-      <c r="C79" s="25"/>
-      <c r="D79" s="16" t="s">
+      <c r="B80" s="25"/>
+      <c r="C80" s="25"/>
+      <c r="D80" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="E79" s="16"/>
-      <c r="F79" s="43" t="s">
+      <c r="E80" s="16"/>
+      <c r="F80" s="43" t="s">
         <v>90</v>
       </c>
-      <c r="G79" s="16" t="s">
+      <c r="G80" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="H79" s="17" t="s">
+      <c r="H80" s="17" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="59"/>
-      <c r="B80" s="12"/>
-      <c r="C80" s="12"/>
-      <c r="D80" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E80" s="1"/>
-      <c r="F80" s="44" t="s">
-        <v>92</v>
-      </c>
-      <c r="G80" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="H80" s="50" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="59"/>
       <c r="B81" s="12"/>
       <c r="C81" s="12"/>
-      <c r="D81" s="1"/>
+      <c r="D81" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="E81" s="1"/>
-      <c r="F81" s="2" t="s">
+      <c r="F81" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H81" s="50" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="59"/>
+      <c r="B82" s="12"/>
+      <c r="C82" s="12"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G81" s="1"/>
-      <c r="H81" s="21"/>
-    </row>
-    <row r="82" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="60"/>
-      <c r="B82" s="26"/>
-      <c r="C82" s="26"/>
-      <c r="D82" s="19"/>
-      <c r="E82" s="19"/>
-      <c r="F82" s="19" t="s">
+      <c r="G82" s="1"/>
+      <c r="H82" s="21"/>
+    </row>
+    <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="60"/>
+      <c r="B83" s="26"/>
+      <c r="C83" s="26"/>
+      <c r="D83" s="19"/>
+      <c r="E83" s="19"/>
+      <c r="F83" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="G82" s="19"/>
-      <c r="H82" s="20"/>
-    </row>
-    <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="14" t="s">
+      <c r="G83" s="19"/>
+      <c r="H83" s="20"/>
+    </row>
+    <row r="84" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="B83" s="16"/>
-      <c r="C83" s="52" t="s">
+      <c r="B84" s="16"/>
+      <c r="C84" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="D83" s="53"/>
-      <c r="E83" s="53"/>
-      <c r="F83" s="53"/>
-      <c r="G83" s="53"/>
-      <c r="H83" s="54"/>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="58" t="s">
+      <c r="D84" s="53"/>
+      <c r="E84" s="53"/>
+      <c r="F84" s="53"/>
+      <c r="G84" s="53"/>
+      <c r="H84" s="54"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="58" t="s">
         <v>96</v>
       </c>
-      <c r="B84" s="16"/>
-      <c r="C84" s="16"/>
-      <c r="D84" s="27" t="s">
+      <c r="B85" s="16"/>
+      <c r="C85" s="16"/>
+      <c r="D85" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="E84" s="16"/>
-      <c r="F84" s="16"/>
-      <c r="G84" s="16"/>
-      <c r="H84" s="17"/>
-    </row>
-    <row r="85" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="62"/>
-      <c r="B85" s="1"/>
-      <c r="C85" s="1"/>
-      <c r="D85" s="28" t="s">
+      <c r="E85" s="16"/>
+      <c r="F85" s="16"/>
+      <c r="G85" s="16"/>
+      <c r="H85" s="17"/>
+    </row>
+    <row r="86" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="62"/>
+      <c r="B86" s="1"/>
+      <c r="C86" s="1"/>
+      <c r="D86" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="E85" s="1"/>
-      <c r="F85" s="1"/>
-      <c r="G85" s="1"/>
-      <c r="H85" s="21"/>
-    </row>
-    <row r="86" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="22" t="s">
-        <v>97</v>
-      </c>
-      <c r="B86" s="52"/>
-      <c r="C86" s="53"/>
-      <c r="D86" s="53"/>
-      <c r="E86" s="53"/>
-      <c r="F86" s="53"/>
-      <c r="G86" s="53"/>
-      <c r="H86" s="54"/>
+      <c r="E86" s="1"/>
+      <c r="F86" s="1"/>
+      <c r="G86" s="1"/>
+      <c r="H86" s="21"/>
     </row>
     <row r="87" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B87" s="52"/>
       <c r="C87" s="53"/>
@@ -7390,117 +7438,117 @@
       <c r="G87" s="53"/>
       <c r="H87" s="54"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="58" t="s">
+    <row r="88" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="B88" s="52"/>
+      <c r="C88" s="53"/>
+      <c r="D88" s="53"/>
+      <c r="E88" s="53"/>
+      <c r="F88" s="53"/>
+      <c r="G88" s="53"/>
+      <c r="H88" s="54"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="58" t="s">
         <v>99</v>
       </c>
-      <c r="B88" s="16"/>
-      <c r="C88" s="16" t="s">
+      <c r="B89" s="16"/>
+      <c r="C89" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="D88" s="16"/>
-      <c r="E88" s="16"/>
-      <c r="F88" s="16" t="s">
+      <c r="D89" s="16"/>
+      <c r="E89" s="16"/>
+      <c r="F89" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="G88" s="35" t="s">
+      <c r="G89" s="35" t="s">
         <v>79</v>
       </c>
-      <c r="H88" s="37" t="s">
+      <c r="H89" s="37" t="s">
         <v>79</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="59"/>
-      <c r="B89" s="1"/>
-      <c r="C89" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D89" s="1"/>
-      <c r="E89" s="1"/>
-      <c r="F89" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G89" s="36" t="s">
-        <v>80</v>
-      </c>
-      <c r="H89" s="38" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="59"/>
       <c r="B90" s="1"/>
-      <c r="C90" s="1"/>
+      <c r="C90" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="D90" s="1"/>
       <c r="E90" s="1"/>
-      <c r="F90" s="1"/>
-      <c r="G90" s="2" t="s">
+      <c r="F90" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G90" s="36" t="s">
+        <v>80</v>
+      </c>
+      <c r="H90" s="38" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="59"/>
+      <c r="B91" s="1"/>
+      <c r="C91" s="1"/>
+      <c r="D91" s="1"/>
+      <c r="E91" s="1"/>
+      <c r="F91" s="1"/>
+      <c r="G91" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H90" s="24" t="s">
+      <c r="H91" s="24" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="91" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="60"/>
-      <c r="B91" s="19"/>
-      <c r="C91" s="19"/>
-      <c r="D91" s="19"/>
-      <c r="E91" s="19"/>
-      <c r="F91" s="19"/>
-      <c r="G91" s="19" t="s">
+    <row r="92" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="60"/>
+      <c r="B92" s="19"/>
+      <c r="C92" s="19"/>
+      <c r="D92" s="19"/>
+      <c r="E92" s="19"/>
+      <c r="F92" s="19"/>
+      <c r="G92" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="H91" s="20" t="s">
+      <c r="H92" s="20" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="58" t="s">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="58" t="s">
         <v>101</v>
       </c>
-      <c r="B92" s="16"/>
-      <c r="C92" s="16"/>
-      <c r="D92" s="27" t="s">
+      <c r="B93" s="16"/>
+      <c r="C93" s="16"/>
+      <c r="D93" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="E92" s="16"/>
-      <c r="F92" s="16"/>
-      <c r="G92" s="27" t="s">
+      <c r="E93" s="16"/>
+      <c r="F93" s="16"/>
+      <c r="G93" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="H92" s="37" t="s">
+      <c r="H93" s="37" t="s">
         <v>79</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="59"/>
-      <c r="B93" s="1"/>
-      <c r="C93" s="1"/>
-      <c r="D93" s="28" t="s">
-        <v>80</v>
-      </c>
-      <c r="E93" s="1"/>
-      <c r="F93" s="1"/>
-      <c r="G93" s="28" t="s">
-        <v>102</v>
-      </c>
-      <c r="H93" s="38" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="59"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
-      <c r="D94" s="28"/>
+      <c r="D94" s="28" t="s">
+        <v>80</v>
+      </c>
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
-      <c r="G94" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="H94" s="66"/>
+      <c r="G94" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="H94" s="38" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="59"/>
@@ -7509,8 +7557,8 @@
       <c r="D95" s="28"/>
       <c r="E95" s="1"/>
       <c r="F95" s="1"/>
-      <c r="G95" s="28" t="s">
-        <v>57</v>
+      <c r="G95" s="30" t="s">
+        <v>12</v>
       </c>
       <c r="H95" s="66"/>
     </row>
@@ -7521,64 +7569,77 @@
       <c r="D96" s="28"/>
       <c r="E96" s="1"/>
       <c r="F96" s="1"/>
-      <c r="G96" s="33" t="s">
+      <c r="G96" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="H96" s="66"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" s="59"/>
+      <c r="B97" s="1"/>
+      <c r="C97" s="1"/>
+      <c r="D97" s="28"/>
+      <c r="E97" s="1"/>
+      <c r="F97" s="1"/>
+      <c r="G97" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="H96" s="66"/>
-    </row>
-    <row r="97" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="60"/>
-      <c r="B97" s="19"/>
-      <c r="C97" s="19"/>
-      <c r="D97" s="29"/>
-      <c r="E97" s="19"/>
-      <c r="F97" s="19"/>
-      <c r="G97" s="34" t="s">
+      <c r="H97" s="66"/>
+    </row>
+    <row r="98" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="60"/>
+      <c r="B98" s="19"/>
+      <c r="C98" s="19"/>
+      <c r="D98" s="29"/>
+      <c r="E98" s="19"/>
+      <c r="F98" s="19"/>
+      <c r="G98" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="H97" s="67"/>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B98" s="61"/>
-      <c r="C98" s="61"/>
-      <c r="D98" s="61"/>
-      <c r="E98" s="61"/>
-      <c r="F98" s="61"/>
-      <c r="G98" s="61"/>
-      <c r="H98" s="61"/>
+      <c r="H98" s="67"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B99" s="61"/>
+      <c r="C99" s="61"/>
+      <c r="D99" s="61"/>
+      <c r="E99" s="61"/>
+      <c r="F99" s="61"/>
+      <c r="G99" s="61"/>
+      <c r="H99" s="61"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="31">
     <mergeCell ref="B1:H1"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B58:H58"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A17:A22"/>
+    <mergeCell ref="A23:A26"/>
+    <mergeCell ref="A27:A36"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="A64:A71"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="A39:A46"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="A49:A56"/>
+    <mergeCell ref="A89:A92"/>
+    <mergeCell ref="A93:A98"/>
+    <mergeCell ref="B99:H99"/>
+    <mergeCell ref="A72:A77"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="A80:A83"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="C84:H84"/>
+    <mergeCell ref="B16:H16"/>
+    <mergeCell ref="B59:H59"/>
     <mergeCell ref="B57:H57"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="A16:A21"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A26:A35"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="A63:A70"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A38:A45"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A48:A55"/>
-    <mergeCell ref="A88:A91"/>
-    <mergeCell ref="A92:A97"/>
-    <mergeCell ref="B98:H98"/>
-    <mergeCell ref="A71:A76"/>
-    <mergeCell ref="A77:A78"/>
-    <mergeCell ref="A79:A82"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="C83:H83"/>
-    <mergeCell ref="B15:H15"/>
-    <mergeCell ref="B58:H58"/>
-    <mergeCell ref="B56:H56"/>
+    <mergeCell ref="B88:H88"/>
     <mergeCell ref="B87:H87"/>
-    <mergeCell ref="B86:H86"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="31" fitToHeight="0" orientation="landscape" r:id="rId1"/>
